--- a/Informes/Gantt Submarino explorador.xlsx
+++ b/Informes/Gantt Submarino explorador.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db7464560a21b141/Documentos/GitHub/ROV-Remotely-Operated-Vehicle-Santamaria-Barrientos/Informes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elcal\Documents\GitHub\ROV-Remotely-Operated-Vehicle-Santamaria-Barrientos\Informes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1376" documentId="8_{078BA771-1572-441F-A369-4555CF5C9A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A01A9EC9-D101-4FED-BE96-BC7A620E88E4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BDB747-C18A-41B1-AA9D-CE2778D737C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{87E74416-7799-4AD7-A0CC-89D4080577C1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{87E74416-7799-4AD7-A0CC-89D4080577C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Tareas_ROV" sheetId="5" r:id="rId2"/>
-    <sheet name="Hoja1 (3)" sheetId="4" r:id="rId3"/>
-    <sheet name="Hoja1 (4)" sheetId="6" r:id="rId4"/>
-    <sheet name="Hoja1 (5)" sheetId="7" r:id="rId5"/>
+    <sheet name="Hoja1 (4)" sheetId="6" r:id="rId3"/>
+    <sheet name="Hoja1 (5)" sheetId="7" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Hoja1 (4)'!$A$2:$BH$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Hoja1 (5)'!$A$2:$CX$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Hoja1 (4)'!$A$2:$BH$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Hoja1 (5)'!$A$2:$CX$33</definedName>
     <definedName name="DatosExternos_1" localSheetId="1" hidden="1">Tareas_ROV!$A$1:$L$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -59,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="215">
   <si>
     <t>TAREA</t>
   </si>
@@ -469,9 +468,6 @@
     <t>Logs + análisis FFT de vibraciones; script de análisis (opcional).</t>
   </si>
   <si>
-    <t>Definición de requisitos y alcance</t>
-  </si>
-  <si>
     <t>Tarea 1.5</t>
   </si>
   <si>
@@ -508,42 +504,9 @@
     <t>Tarea 2.4</t>
   </si>
   <si>
-    <t>TESTEO</t>
-  </si>
-  <si>
     <t>Tarea 3.6</t>
   </si>
   <si>
-    <t>Tarea 3.7</t>
-  </si>
-  <si>
-    <t>Tarea 3.8</t>
-  </si>
-  <si>
-    <t>Prueba y ajuste cámara + balance de blancos + luces</t>
-  </si>
-  <si>
-    <t>ajustar exposición, correción para agua, drivers de LEDs y control de potencia.</t>
-  </si>
-  <si>
-    <t>T12;T11</t>
-  </si>
-  <si>
-    <t>DOCUMENTACIÓN Y PRESENTACIÓN</t>
-  </si>
-  <si>
-    <t>Tarea 4.1</t>
-  </si>
-  <si>
-    <t>Tarea 4.2</t>
-  </si>
-  <si>
-    <t>Tarea 4.3</t>
-  </si>
-  <si>
-    <t>Tarea 4.4</t>
-  </si>
-  <si>
     <t>DÍAS</t>
   </si>
   <si>
@@ -556,12 +519,6 @@
     <t>ROV SUBMARINO</t>
   </si>
   <si>
-    <t>Mauro Ramiro Barrientos 37040805</t>
-  </si>
-  <si>
-    <t>Alvaro Santamaria 40514994</t>
-  </si>
-  <si>
     <t>Prueba y programación del MPU-6050</t>
   </si>
   <si>
@@ -745,10 +702,7 @@
     <t>ROV PARA INSPECCIÓN SUBACUÁTICA</t>
   </si>
   <si>
-    <t>Llega el sensor de presión el 16/09</t>
-  </si>
-  <si>
-    <t>Llegan los drivers el 16/09 y los motores el 17/09</t>
+    <t>31/04/2026</t>
   </si>
 </sst>
 </file>
@@ -925,7 +879,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -964,13 +918,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -993,19 +940,19 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1014,20 +961,20 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="36">
     <dxf>
       <fill>
         <patternFill>
@@ -1263,32 +1210,6 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FFFF0000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFFF0000"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -1304,10 +1225,10 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
+      <numFmt numFmtId="167" formatCode="d/m/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
+      <numFmt numFmtId="167" formatCode="d/m/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1333,14 +1254,10 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="$B$6" horiz="1" max="100" page="10" val="26"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="$B$6" horiz="1" max="80" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="$B$6" horiz="1" max="80" page="10" val="0"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="26" fmlaLink="$B$6" horiz="1" max="80" page="10" val="0"/>
 </file>
 
@@ -1418,61 +1335,6 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4097" name="Scroll Bar 1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4097"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a:ln>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
             <xdr:cNvPr id="6145" name="Scroll Bar 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
@@ -1509,7 +1371,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -1593,18 +1455,18 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D64B082-EBDE-4B94-B5DA-B5C2B24E06DA}" name="Tareas_ROV" displayName="Tareas_ROV" ref="A1:L26" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:L26" xr:uid="{5D64B082-EBDE-4B94-B5DA-B5C2B24E06DA}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{E6CD7D62-2A43-4D44-90D0-DAEDEB34F84F}" uniqueName="1" name="ID" queryTableFieldId="1" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{EE1FB163-6A07-407B-80F7-B12146176EC3}" uniqueName="2" name="Task" queryTableFieldId="2" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{470AD21C-7EFC-46C0-AADA-02F55C00AA29}" uniqueName="3" name="Start" queryTableFieldId="3" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{CDC18EB9-16A1-4564-8830-DFC635ADA40B}" uniqueName="4" name="End" queryTableFieldId="4" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{E6CD7D62-2A43-4D44-90D0-DAEDEB34F84F}" uniqueName="1" name="ID" queryTableFieldId="1" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{EE1FB163-6A07-407B-80F7-B12146176EC3}" uniqueName="2" name="Task" queryTableFieldId="2" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{470AD21C-7EFC-46C0-AADA-02F55C00AA29}" uniqueName="3" name="Start" queryTableFieldId="3" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{CDC18EB9-16A1-4564-8830-DFC635ADA40B}" uniqueName="4" name="End" queryTableFieldId="4" dataDxfId="32"/>
     <tableColumn id="5" xr3:uid="{6D5A5D46-1B4F-4274-80A5-2C1237549F4C}" uniqueName="5" name="DurationDays" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{7B96CDE1-B265-44DC-9A44-2C5B4C9D3C7D}" uniqueName="6" name="HoursEstimated" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{79575DA2-6425-4193-BAFF-1D67141BCE22}" uniqueName="7" name="DependsOn" queryTableFieldId="7" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{4F345EDF-4C8F-45F7-8C3F-323777D716BD}" uniqueName="8" name="Responsible" queryTableFieldId="8" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{79575DA2-6425-4193-BAFF-1D67141BCE22}" uniqueName="7" name="DependsOn" queryTableFieldId="7" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{4F345EDF-4C8F-45F7-8C3F-323777D716BD}" uniqueName="8" name="Responsible" queryTableFieldId="8" dataDxfId="30"/>
     <tableColumn id="9" xr3:uid="{759194FA-BC37-440E-B424-1DA9E377DCF7}" uniqueName="9" name="PercentComplete" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{13D304DC-FAF8-4CA3-9885-308E2C77E7FE}" uniqueName="10" name="HoursReal" queryTableFieldId="10" dataDxfId="32"/>
-    <tableColumn id="11" xr3:uid="{EFFAC105-8C0D-4937-985A-31AE84B0FAEE}" uniqueName="11" name="Description" queryTableFieldId="11" dataDxfId="31"/>
-    <tableColumn id="12" xr3:uid="{8452A1A4-7D9F-4DDB-8A5E-A4050DC7C96A}" uniqueName="12" name="Notes" queryTableFieldId="12" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{13D304DC-FAF8-4CA3-9885-308E2C77E7FE}" uniqueName="10" name="HoursReal" queryTableFieldId="10" dataDxfId="29"/>
+    <tableColumn id="11" xr3:uid="{EFFAC105-8C0D-4937-985A-31AE84B0FAEE}" uniqueName="11" name="Description" queryTableFieldId="11" dataDxfId="28"/>
+    <tableColumn id="12" xr3:uid="{8452A1A4-7D9F-4DDB-8A5E-A4050DC7C96A}" uniqueName="12" name="Notes" queryTableFieldId="12" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1928,201 +1790,201 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6118F328-76F0-48AF-8693-8E0C2425A51D}">
   <dimension ref="A1:AJ22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="15.77734375" customWidth="1"/>
-    <col min="3" max="5" width="11.77734375" customWidth="1"/>
-    <col min="7" max="34" width="3.77734375" customWidth="1"/>
+    <col min="1" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="5" width="11.7109375" customWidth="1"/>
+    <col min="7" max="34" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="AJ1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="AJ2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="AJ3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="D4">
         <v>100</v>
       </c>
       <c r="E4" s="3">
         <f>D5+D4</f>
-        <v>45991</v>
-      </c>
-      <c r="G4" s="33">
+        <v>46218</v>
+      </c>
+      <c r="G4" s="31">
         <f>G5</f>
-        <v>45991</v>
-      </c>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33">
+        <v>46218</v>
+      </c>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31">
         <f>N5</f>
-        <v>45998</v>
-      </c>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33">
+        <v>46225</v>
+      </c>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31">
         <f>U5</f>
-        <v>46005</v>
-      </c>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="33"/>
-      <c r="AA4" s="33"/>
-      <c r="AB4" s="33">
+        <v>46232</v>
+      </c>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="31">
         <f>AB5</f>
-        <v>46012</v>
-      </c>
-      <c r="AC4" s="33"/>
-      <c r="AD4" s="33"/>
-      <c r="AE4" s="33"/>
-      <c r="AF4" s="33"/>
-      <c r="AG4" s="33"/>
-      <c r="AH4" s="33"/>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="B5" s="34" t="s">
+        <v>46239</v>
+      </c>
+      <c r="AC4" s="31"/>
+      <c r="AD4" s="31"/>
+      <c r="AE4" s="31"/>
+      <c r="AF4" s="31"/>
+      <c r="AG4" s="31"/>
+      <c r="AH4" s="31"/>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="B5" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="35">
-        <v>45891</v>
-      </c>
-      <c r="E5" s="35"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="33">
+        <v>46118</v>
+      </c>
+      <c r="E5" s="33"/>
       <c r="F5" s="1"/>
       <c r="G5" s="4">
         <f>E4</f>
-        <v>45991</v>
+        <v>46218</v>
       </c>
       <c r="H5" s="4">
         <f>G5+1</f>
-        <v>45992</v>
+        <v>46219</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" ref="I5:W5" si="0">H5+1</f>
-        <v>45993</v>
+        <v>46220</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="0"/>
-        <v>45994</v>
+        <v>46221</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="0"/>
-        <v>45995</v>
+        <v>46222</v>
       </c>
       <c r="L5" s="4">
         <f t="shared" si="0"/>
-        <v>45996</v>
+        <v>46223</v>
       </c>
       <c r="M5" s="4">
         <f t="shared" si="0"/>
-        <v>45997</v>
+        <v>46224</v>
       </c>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>45998</v>
+        <v>46225</v>
       </c>
       <c r="O5" s="4">
         <f t="shared" si="0"/>
-        <v>45999</v>
+        <v>46226</v>
       </c>
       <c r="P5" s="4">
         <f t="shared" si="0"/>
-        <v>46000</v>
+        <v>46227</v>
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>46001</v>
+        <v>46228</v>
       </c>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>46002</v>
+        <v>46229</v>
       </c>
       <c r="S5" s="4">
         <f t="shared" si="0"/>
-        <v>46003</v>
+        <v>46230</v>
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
-        <v>46004</v>
+        <v>46231</v>
       </c>
       <c r="U5" s="4">
         <f t="shared" si="0"/>
-        <v>46005</v>
+        <v>46232</v>
       </c>
       <c r="V5" s="4">
         <f t="shared" si="0"/>
-        <v>46006</v>
+        <v>46233</v>
       </c>
       <c r="W5" s="4">
         <f t="shared" si="0"/>
-        <v>46007</v>
+        <v>46234</v>
       </c>
       <c r="X5" s="4">
         <f>W5+1</f>
-        <v>46008</v>
+        <v>46235</v>
       </c>
       <c r="Y5" s="4">
         <f t="shared" ref="Y5:AC5" si="1">X5+1</f>
-        <v>46009</v>
+        <v>46236</v>
       </c>
       <c r="Z5" s="4">
         <f t="shared" si="1"/>
-        <v>46010</v>
+        <v>46237</v>
       </c>
       <c r="AA5" s="4">
         <f t="shared" si="1"/>
-        <v>46011</v>
+        <v>46238</v>
       </c>
       <c r="AB5" s="4">
         <f t="shared" si="1"/>
-        <v>46012</v>
+        <v>46239</v>
       </c>
       <c r="AC5" s="4">
         <f t="shared" si="1"/>
-        <v>46013</v>
+        <v>46240</v>
       </c>
       <c r="AD5" s="4">
         <f t="shared" ref="AD5:AF5" si="2">AC5+1</f>
-        <v>46014</v>
+        <v>46241</v>
       </c>
       <c r="AE5" s="4">
         <f t="shared" si="2"/>
-        <v>46015</v>
+        <v>46242</v>
       </c>
       <c r="AF5" s="4">
         <f t="shared" si="2"/>
-        <v>46016</v>
+        <v>46243</v>
       </c>
       <c r="AG5" s="4">
         <f t="shared" ref="AG5:AH5" si="3">AF5+1</f>
-        <v>46017</v>
+        <v>46244</v>
       </c>
       <c r="AH5" s="4">
         <f t="shared" si="3"/>
-        <v>46018</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -2141,118 +2003,118 @@
       <c r="F6" s="5"/>
       <c r="G6" s="6" t="str">
         <f>UPPER(LEFT(TEXT(G5,"ddd"),1))</f>
-        <v>D</v>
+        <v>M</v>
       </c>
       <c r="H6" s="6" t="str">
         <f t="shared" ref="H6:AC6" si="4">UPPER(LEFT(TEXT(H5,"ddd"),1))</f>
-        <v>L</v>
+        <v>J</v>
       </c>
       <c r="I6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>M</v>
+        <v>V</v>
       </c>
       <c r="J6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="K6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>J</v>
+        <v>D</v>
       </c>
       <c r="L6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>V</v>
+        <v>L</v>
       </c>
       <c r="M6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="N6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>D</v>
+        <v>M</v>
       </c>
       <c r="O6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>L</v>
+        <v>J</v>
       </c>
       <c r="P6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>M</v>
+        <v>V</v>
       </c>
       <c r="Q6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="R6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>J</v>
+        <v>D</v>
       </c>
       <c r="S6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>V</v>
+        <v>L</v>
       </c>
       <c r="T6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="U6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>D</v>
+        <v>M</v>
       </c>
       <c r="V6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>L</v>
+        <v>J</v>
       </c>
       <c r="W6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>M</v>
+        <v>V</v>
       </c>
       <c r="X6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="Y6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>J</v>
+        <v>D</v>
       </c>
       <c r="Z6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>V</v>
+        <v>L</v>
       </c>
       <c r="AA6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AB6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>D</v>
+        <v>M</v>
       </c>
       <c r="AC6" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>L</v>
+        <v>J</v>
       </c>
       <c r="AD6" s="6" t="str">
         <f t="shared" ref="AD6" si="5">UPPER(LEFT(TEXT(AD5,"ddd"),1))</f>
-        <v>M</v>
+        <v>V</v>
       </c>
       <c r="AE6" s="6" t="str">
         <f t="shared" ref="AE6" si="6">UPPER(LEFT(TEXT(AE5,"ddd"),1))</f>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="AF6" s="6" t="str">
         <f t="shared" ref="AF6" si="7">UPPER(LEFT(TEXT(AF5,"ddd"),1))</f>
-        <v>J</v>
+        <v>D</v>
       </c>
       <c r="AG6" s="6" t="str">
         <f t="shared" ref="AG6" si="8">UPPER(LEFT(TEXT(AG5,"ddd"),1))</f>
-        <v>V</v>
+        <v>L</v>
       </c>
       <c r="AH6" s="6" t="str">
         <f t="shared" ref="AH6" si="9">UPPER(LEFT(TEXT(AH5,"ddd"),1))</f>
-        <v>S</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>24</v>
       </c>
@@ -2290,7 +2152,7 @@
       <c r="AG7" s="8"/>
       <c r="AH7" s="8"/>
     </row>
-    <row r="8" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>5</v>
       </c>
@@ -2301,10 +2163,10 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="10">
-        <v>45889</v>
+        <v>46118</v>
       </c>
       <c r="E8" s="10">
-        <v>45894</v>
+        <v>46123</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -2336,7 +2198,7 @@
       <c r="AG8" s="8"/>
       <c r="AH8" s="8"/>
     </row>
-    <row r="9" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
@@ -2347,10 +2209,10 @@
         <v>0.2</v>
       </c>
       <c r="D9" s="10">
-        <v>45890</v>
+        <v>46129</v>
       </c>
       <c r="E9" s="10">
-        <v>45895</v>
+        <v>46134</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -2382,7 +2244,7 @@
       <c r="AG9" s="8"/>
       <c r="AH9" s="8"/>
     </row>
-    <row r="10" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>7</v>
       </c>
@@ -2393,10 +2255,10 @@
         <v>1</v>
       </c>
       <c r="D10" s="10">
-        <v>45891</v>
+        <v>46130</v>
       </c>
       <c r="E10" s="10">
-        <v>45896</v>
+        <v>46135</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -2428,7 +2290,7 @@
       <c r="AG10" s="8"/>
       <c r="AH10" s="8"/>
     </row>
-    <row r="11" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
         <v>9</v>
@@ -2466,7 +2328,7 @@
       <c r="AG11" s="8"/>
       <c r="AH11" s="8"/>
     </row>
-    <row r="12" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>8</v>
       </c>
@@ -2477,10 +2339,10 @@
         <v>1</v>
       </c>
       <c r="D12" s="10">
-        <v>45892</v>
+        <v>46135</v>
       </c>
       <c r="E12" s="10">
-        <v>45897</v>
+        <v>46140</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
@@ -2512,7 +2374,7 @@
       <c r="AG12" s="8"/>
       <c r="AH12" s="8"/>
     </row>
-    <row r="13" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
@@ -2550,7 +2412,7 @@
       <c r="AG13" s="8"/>
       <c r="AH13" s="8"/>
     </row>
-    <row r="14" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
@@ -2561,10 +2423,10 @@
         <v>0.3</v>
       </c>
       <c r="D14" s="10">
-        <v>45894</v>
+        <v>46137</v>
       </c>
       <c r="E14" s="10">
-        <v>45899</v>
+        <v>46142</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
@@ -2596,7 +2458,7 @@
       <c r="AG14" s="8"/>
       <c r="AH14" s="8"/>
     </row>
-    <row r="15" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>12</v>
       </c>
@@ -2607,10 +2469,10 @@
         <v>0.5</v>
       </c>
       <c r="D15" s="10">
-        <v>45895</v>
-      </c>
-      <c r="E15" s="10">
-        <v>45900</v>
+        <v>46138</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>214</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
@@ -2642,7 +2504,7 @@
       <c r="AG15" s="8"/>
       <c r="AH15" s="8"/>
     </row>
-    <row r="16" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>13</v>
       </c>
@@ -2653,10 +2515,10 @@
         <v>0.1</v>
       </c>
       <c r="D16" s="10">
-        <v>45896</v>
+        <v>46139</v>
       </c>
       <c r="E16" s="10">
-        <v>45901</v>
+        <v>46113</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
@@ -2688,7 +2550,7 @@
       <c r="AG16" s="8"/>
       <c r="AH16" s="8"/>
     </row>
-    <row r="17" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>14</v>
       </c>
@@ -2726,7 +2588,7 @@
       <c r="AG17" s="8"/>
       <c r="AH17" s="8"/>
     </row>
-    <row r="18" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>15</v>
       </c>
@@ -2737,10 +2599,10 @@
         <v>0.8</v>
       </c>
       <c r="D18" s="10">
-        <v>45898</v>
+        <v>46141</v>
       </c>
       <c r="E18" s="10">
-        <v>45903</v>
+        <v>46145</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
@@ -2772,7 +2634,7 @@
       <c r="AG18" s="8"/>
       <c r="AH18" s="8"/>
     </row>
-    <row r="19" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>16</v>
       </c>
@@ -2783,10 +2645,10 @@
         <v>0.9</v>
       </c>
       <c r="D19" s="10">
-        <v>45899</v>
+        <v>46142</v>
       </c>
       <c r="E19" s="10">
-        <v>45904</v>
+        <v>46146</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
@@ -2818,7 +2680,7 @@
       <c r="AG19" s="8"/>
       <c r="AH19" s="8"/>
     </row>
-    <row r="20" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>17</v>
       </c>
@@ -2828,11 +2690,11 @@
       <c r="C20" s="9">
         <v>0.5</v>
       </c>
-      <c r="D20" s="10">
-        <v>45900</v>
+      <c r="D20" s="10" t="s">
+        <v>214</v>
       </c>
       <c r="E20" s="10">
-        <v>45905</v>
+        <v>46147</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
@@ -2864,7 +2726,7 @@
       <c r="AG20" s="8"/>
       <c r="AH20" s="8"/>
     </row>
-    <row r="21" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>18</v>
       </c>
@@ -2875,10 +2737,10 @@
         <v>0.65</v>
       </c>
       <c r="D21" s="10">
-        <v>45901</v>
+        <v>46143</v>
       </c>
       <c r="E21" s="10">
-        <v>45906</v>
+        <v>46148</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
@@ -2910,7 +2772,7 @@
       <c r="AG21" s="8"/>
       <c r="AH21" s="8"/>
     </row>
-    <row r="22" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>19</v>
       </c>
@@ -2921,10 +2783,10 @@
         <v>0.7</v>
       </c>
       <c r="D22" s="10">
-        <v>45902</v>
+        <v>46144</v>
       </c>
       <c r="E22" s="10">
-        <v>45907</v>
+        <v>46149</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
@@ -2981,13 +2843,13 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:AH22">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>G$5=TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="2">
+    <cfRule type="expression" dxfId="25" priority="2">
       <formula>AND(G$5&gt;=$D7,G$5&lt;=((($E7-$D7+1)*$C7)+$D7-1))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="3">
+    <cfRule type="expression" dxfId="24" priority="3">
       <formula>AND(G$5&gt;=$D7,G$5&lt;=$E7)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3051,22 +2913,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F533DFE3-7993-4042-9066-14B6FC10C11C}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="80.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="80.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -3104,7 +2966,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -3112,10 +2974,10 @@
         <v>39</v>
       </c>
       <c r="C2" s="11">
-        <v>45891</v>
+        <v>46134</v>
       </c>
       <c r="D2" s="11">
-        <v>45892</v>
+        <v>46135</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3142,7 +3004,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -3150,10 +3012,10 @@
         <v>43</v>
       </c>
       <c r="C3" s="11">
-        <v>45893</v>
+        <v>46136</v>
       </c>
       <c r="D3" s="11">
-        <v>45894</v>
+        <v>46137</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3180,7 +3042,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -3188,10 +3050,10 @@
         <v>47</v>
       </c>
       <c r="C4" s="11">
-        <v>45895</v>
+        <v>46138</v>
       </c>
       <c r="D4" s="11">
-        <v>45901</v>
+        <v>46143</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -3218,7 +3080,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -3226,10 +3088,10 @@
         <v>51</v>
       </c>
       <c r="C5" s="11">
-        <v>45902</v>
+        <v>46144</v>
       </c>
       <c r="D5" s="11">
-        <v>45904</v>
+        <v>46146</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -3256,7 +3118,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>54</v>
       </c>
@@ -3264,10 +3126,10 @@
         <v>55</v>
       </c>
       <c r="C6" s="11">
-        <v>45905</v>
+        <v>46147</v>
       </c>
       <c r="D6" s="11">
-        <v>45906</v>
+        <v>46148</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -3294,7 +3156,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>59</v>
       </c>
@@ -3302,10 +3164,10 @@
         <v>60</v>
       </c>
       <c r="C7" s="11">
-        <v>45907</v>
+        <v>46149</v>
       </c>
       <c r="D7" s="11">
-        <v>45910</v>
+        <v>46152</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -3332,7 +3194,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>62</v>
       </c>
@@ -3340,10 +3202,10 @@
         <v>63</v>
       </c>
       <c r="C8" s="11">
-        <v>45911</v>
+        <v>46153</v>
       </c>
       <c r="D8" s="11">
-        <v>45912</v>
+        <v>46154</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -3370,7 +3232,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -3378,10 +3240,10 @@
         <v>67</v>
       </c>
       <c r="C9" s="11">
-        <v>45911</v>
+        <v>46153</v>
       </c>
       <c r="D9" s="11">
-        <v>45917</v>
+        <v>46159</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -3408,7 +3270,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>71</v>
       </c>
@@ -3416,10 +3278,10 @@
         <v>72</v>
       </c>
       <c r="C10" s="11">
-        <v>45913</v>
+        <v>46155</v>
       </c>
       <c r="D10" s="11">
-        <v>45914</v>
+        <v>46156</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -3446,7 +3308,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>75</v>
       </c>
@@ -3454,10 +3316,10 @@
         <v>76</v>
       </c>
       <c r="C11" s="11">
-        <v>45915</v>
+        <v>46157</v>
       </c>
       <c r="D11" s="11">
-        <v>45916</v>
+        <v>46158</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -3484,7 +3346,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>79</v>
       </c>
@@ -3492,10 +3354,10 @@
         <v>80</v>
       </c>
       <c r="C12" s="11">
-        <v>45918</v>
+        <v>46160</v>
       </c>
       <c r="D12" s="11">
-        <v>45918</v>
+        <v>46160</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3522,7 +3384,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -3530,10 +3392,10 @@
         <v>83</v>
       </c>
       <c r="C13" s="11">
-        <v>45919</v>
+        <v>46161</v>
       </c>
       <c r="D13" s="11">
-        <v>45922</v>
+        <v>46164</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -3560,7 +3422,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>86</v>
       </c>
@@ -3568,10 +3430,10 @@
         <v>87</v>
       </c>
       <c r="C14" s="11">
-        <v>45923</v>
+        <v>46165</v>
       </c>
       <c r="D14" s="11">
-        <v>45924</v>
+        <v>46166</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -3598,7 +3460,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -3606,10 +3468,10 @@
         <v>90</v>
       </c>
       <c r="C15" s="11">
-        <v>45925</v>
+        <v>46167</v>
       </c>
       <c r="D15" s="11">
-        <v>45925</v>
+        <v>46167</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -3636,7 +3498,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -3644,10 +3506,10 @@
         <v>95</v>
       </c>
       <c r="C16" s="11">
-        <v>45926</v>
+        <v>46168</v>
       </c>
       <c r="D16" s="11">
-        <v>45927</v>
+        <v>46169</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -3674,7 +3536,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -3682,10 +3544,10 @@
         <v>99</v>
       </c>
       <c r="C17" s="11">
-        <v>45931</v>
+        <v>46174</v>
       </c>
       <c r="D17" s="11">
-        <v>45931</v>
+        <v>46174</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -3712,7 +3574,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>101</v>
       </c>
@@ -3720,10 +3582,10 @@
         <v>102</v>
       </c>
       <c r="C18" s="11">
-        <v>45932</v>
+        <v>46175</v>
       </c>
       <c r="D18" s="11">
-        <v>45932</v>
+        <v>46175</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -3750,7 +3612,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>104</v>
       </c>
@@ -3758,10 +3620,10 @@
         <v>105</v>
       </c>
       <c r="C19" s="11">
-        <v>45933</v>
+        <v>46176</v>
       </c>
       <c r="D19" s="11">
-        <v>45933</v>
+        <v>46176</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -3788,7 +3650,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>108</v>
       </c>
@@ -3796,10 +3658,10 @@
         <v>109</v>
       </c>
       <c r="C20" s="11">
-        <v>45964</v>
+        <v>46206</v>
       </c>
       <c r="D20" s="11">
-        <v>45966</v>
+        <v>46208</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -3826,7 +3688,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -3834,10 +3696,10 @@
         <v>113</v>
       </c>
       <c r="C21" s="11">
-        <v>45967</v>
+        <v>46209</v>
       </c>
       <c r="D21" s="11">
-        <v>45967</v>
+        <v>46209</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -3864,7 +3726,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>116</v>
       </c>
@@ -3872,10 +3734,10 @@
         <v>117</v>
       </c>
       <c r="C22" s="11">
-        <v>45968</v>
+        <v>46210</v>
       </c>
       <c r="D22" s="11">
-        <v>45971</v>
+        <v>46213</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -3902,7 +3764,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>120</v>
       </c>
@@ -3910,10 +3772,10 @@
         <v>121</v>
       </c>
       <c r="C23" s="11">
-        <v>45973</v>
+        <v>46215</v>
       </c>
       <c r="D23" s="11">
-        <v>45973</v>
+        <v>46215</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -3940,7 +3802,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>124</v>
       </c>
@@ -3948,10 +3810,10 @@
         <v>125</v>
       </c>
       <c r="C24" s="11">
-        <v>45944</v>
+        <v>46187</v>
       </c>
       <c r="D24" s="11">
-        <v>45945</v>
+        <v>46188</v>
       </c>
       <c r="E24">
         <v>2</v>
@@ -3978,7 +3840,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>128</v>
       </c>
@@ -3986,10 +3848,10 @@
         <v>129</v>
       </c>
       <c r="C25" s="11">
-        <v>45946</v>
+        <v>46189</v>
       </c>
       <c r="D25" s="11">
-        <v>45947</v>
+        <v>46190</v>
       </c>
       <c r="E25">
         <v>2</v>
@@ -4016,7 +3878,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>132</v>
       </c>
@@ -4024,10 +3886,10 @@
         <v>133</v>
       </c>
       <c r="C26" s="11">
-        <v>45950</v>
+        <v>46193</v>
       </c>
       <c r="D26" s="11">
-        <v>45951</v>
+        <v>46194</v>
       </c>
       <c r="E26">
         <v>2</v>
@@ -4063,134 +3925,145 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5687727A-AA86-40DD-BC79-EDD06B7F5A9F}">
-  <dimension ref="A1:BH45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF802CD8-39A9-4ECD-ACA4-4544CF43688C}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="45.77734375" customWidth="1"/>
-    <col min="4" max="5" width="12.77734375" style="1" customWidth="1"/>
-    <col min="6" max="7" width="10.77734375" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" customWidth="1"/>
-    <col min="10" max="10" width="14.77734375" customWidth="1"/>
-    <col min="11" max="14" width="10.33203125" customWidth="1"/>
-    <col min="15" max="16" width="20.77734375" customWidth="1"/>
-    <col min="17" max="18" width="11.77734375" customWidth="1"/>
-    <col min="19" max="60" width="3.77734375" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" customWidth="1"/>
+    <col min="4" max="5" width="10.7109375" style="1" customWidth="1"/>
+    <col min="6" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.28515625" customWidth="1"/>
+    <col min="15" max="16" width="20.7109375" customWidth="1"/>
+    <col min="17" max="18" width="11.7109375" customWidth="1"/>
+    <col min="19" max="60" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" s="15" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:60" s="15" customFormat="1" ht="36.6" x14ac:dyDescent="0.3">
-      <c r="C2" s="18" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="1:60" ht="21" x14ac:dyDescent="0.3">
-      <c r="C3" s="20" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="4" spans="1:60" ht="21" x14ac:dyDescent="0.4">
-      <c r="C4" s="19" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:60" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:60" s="15" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+    </row>
+    <row r="3" spans="1:60" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+    </row>
+    <row r="4" spans="1:60" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+    </row>
+    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
       <c r="B6">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3">
         <f>D7+B6</f>
-        <v>45917</v>
-      </c>
-      <c r="F6" s="36" t="s">
+        <v>46113</v>
+      </c>
+      <c r="F6" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="K6" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="K6" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="Q6" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="R6" s="36"/>
-      <c r="S6" s="33">
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="37"/>
+      <c r="Q6" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="R6" s="37"/>
+      <c r="S6" s="31">
         <f>S7</f>
-        <v>45917</v>
-      </c>
-      <c r="T6" s="33"/>
-      <c r="U6" s="33"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33">
+        <v>46113</v>
+      </c>
+      <c r="T6" s="31"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="31"/>
+      <c r="Y6" s="31"/>
+      <c r="Z6" s="31">
         <f>Z7</f>
-        <v>45924</v>
-      </c>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="33"/>
-      <c r="AE6" s="33"/>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="33">
+        <v>46120</v>
+      </c>
+      <c r="AA6" s="31"/>
+      <c r="AB6" s="31"/>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="31"/>
+      <c r="AE6" s="31"/>
+      <c r="AF6" s="31"/>
+      <c r="AG6" s="31">
         <f>AG7</f>
-        <v>45931</v>
-      </c>
-      <c r="AH6" s="33"/>
-      <c r="AI6" s="33"/>
-      <c r="AJ6" s="33"/>
-      <c r="AK6" s="33"/>
-      <c r="AL6" s="33"/>
-      <c r="AM6" s="33"/>
-      <c r="AN6" s="33">
+        <v>46127</v>
+      </c>
+      <c r="AH6" s="31"/>
+      <c r="AI6" s="31"/>
+      <c r="AJ6" s="31"/>
+      <c r="AK6" s="31"/>
+      <c r="AL6" s="31"/>
+      <c r="AM6" s="31"/>
+      <c r="AN6" s="31">
         <f>AN7</f>
-        <v>45938</v>
-      </c>
-      <c r="AO6" s="33"/>
-      <c r="AP6" s="33"/>
-      <c r="AQ6" s="33"/>
-      <c r="AR6" s="33"/>
-      <c r="AS6" s="33"/>
-      <c r="AT6" s="33"/>
-      <c r="AU6" s="33">
+        <v>46134</v>
+      </c>
+      <c r="AO6" s="31"/>
+      <c r="AP6" s="31"/>
+      <c r="AQ6" s="31"/>
+      <c r="AR6" s="31"/>
+      <c r="AS6" s="31"/>
+      <c r="AT6" s="31"/>
+      <c r="AU6" s="31">
         <f>AU7</f>
-        <v>45945</v>
-      </c>
-      <c r="AV6" s="33"/>
-      <c r="AW6" s="33"/>
-      <c r="AX6" s="33"/>
-      <c r="AY6" s="33"/>
-      <c r="AZ6" s="33"/>
-      <c r="BA6" s="33"/>
-      <c r="BB6" s="33">
+        <v>46141</v>
+      </c>
+      <c r="AV6" s="31"/>
+      <c r="AW6" s="31"/>
+      <c r="AX6" s="31"/>
+      <c r="AY6" s="31"/>
+      <c r="AZ6" s="31"/>
+      <c r="BA6" s="31"/>
+      <c r="BB6" s="31">
         <f>BB7</f>
-        <v>45952</v>
-      </c>
-      <c r="BC6" s="33"/>
-      <c r="BD6" s="33"/>
-      <c r="BE6" s="33"/>
-      <c r="BF6" s="33"/>
-      <c r="BG6" s="33"/>
-      <c r="BH6" s="33"/>
-    </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="B7" s="37" t="s">
+        <v>46148</v>
+      </c>
+      <c r="BC6" s="31"/>
+      <c r="BD6" s="31"/>
+      <c r="BE6" s="31"/>
+      <c r="BF6" s="31"/>
+      <c r="BG6" s="31"/>
+      <c r="BH6" s="31"/>
+    </row>
+    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="B7" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="35">
-        <v>45891</v>
-      </c>
-      <c r="E7" s="35"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33">
+        <v>46113</v>
+      </c>
+      <c r="E7" s="33"/>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -4206,176 +4079,176 @@
       <c r="R7" s="17"/>
       <c r="S7" s="4">
         <f>C6</f>
-        <v>45917</v>
+        <v>46113</v>
       </c>
       <c r="T7" s="4">
         <f>S7+1</f>
-        <v>45918</v>
+        <v>46114</v>
       </c>
       <c r="U7" s="4">
         <f t="shared" ref="U7:AI7" si="0">T7+1</f>
-        <v>45919</v>
+        <v>46115</v>
       </c>
       <c r="V7" s="4">
         <f t="shared" si="0"/>
-        <v>45920</v>
+        <v>46116</v>
       </c>
       <c r="W7" s="4">
         <f t="shared" si="0"/>
-        <v>45921</v>
+        <v>46117</v>
       </c>
       <c r="X7" s="4">
         <f t="shared" si="0"/>
-        <v>45922</v>
+        <v>46118</v>
       </c>
       <c r="Y7" s="4">
         <f t="shared" si="0"/>
-        <v>45923</v>
+        <v>46119</v>
       </c>
       <c r="Z7" s="4">
         <f t="shared" si="0"/>
-        <v>45924</v>
+        <v>46120</v>
       </c>
       <c r="AA7" s="4">
         <f t="shared" si="0"/>
-        <v>45925</v>
+        <v>46121</v>
       </c>
       <c r="AB7" s="4">
         <f t="shared" si="0"/>
-        <v>45926</v>
+        <v>46122</v>
       </c>
       <c r="AC7" s="4">
         <f t="shared" si="0"/>
-        <v>45927</v>
+        <v>46123</v>
       </c>
       <c r="AD7" s="4">
         <f t="shared" si="0"/>
-        <v>45928</v>
+        <v>46124</v>
       </c>
       <c r="AE7" s="4">
         <f t="shared" si="0"/>
-        <v>45929</v>
+        <v>46125</v>
       </c>
       <c r="AF7" s="4">
         <f t="shared" si="0"/>
-        <v>45930</v>
+        <v>46126</v>
       </c>
       <c r="AG7" s="4">
         <f t="shared" si="0"/>
-        <v>45931</v>
+        <v>46127</v>
       </c>
       <c r="AH7" s="4">
         <f t="shared" si="0"/>
-        <v>45932</v>
+        <v>46128</v>
       </c>
       <c r="AI7" s="4">
         <f t="shared" si="0"/>
-        <v>45933</v>
+        <v>46129</v>
       </c>
       <c r="AJ7" s="4">
         <f>AI7+1</f>
-        <v>45934</v>
+        <v>46130</v>
       </c>
       <c r="AK7" s="4">
-        <f t="shared" ref="AK7:AT7" si="1">AJ7+1</f>
-        <v>45935</v>
+        <f t="shared" ref="AK7:BH7" si="1">AJ7+1</f>
+        <v>46131</v>
       </c>
       <c r="AL7" s="4">
         <f t="shared" si="1"/>
-        <v>45936</v>
+        <v>46132</v>
       </c>
       <c r="AM7" s="4">
         <f t="shared" si="1"/>
-        <v>45937</v>
+        <v>46133</v>
       </c>
       <c r="AN7" s="4">
         <f t="shared" si="1"/>
-        <v>45938</v>
+        <v>46134</v>
       </c>
       <c r="AO7" s="4">
         <f t="shared" si="1"/>
-        <v>45939</v>
+        <v>46135</v>
       </c>
       <c r="AP7" s="4">
         <f t="shared" si="1"/>
-        <v>45940</v>
+        <v>46136</v>
       </c>
       <c r="AQ7" s="4">
         <f t="shared" si="1"/>
-        <v>45941</v>
+        <v>46137</v>
       </c>
       <c r="AR7" s="4">
         <f t="shared" si="1"/>
-        <v>45942</v>
+        <v>46138</v>
       </c>
       <c r="AS7" s="4">
         <f t="shared" si="1"/>
-        <v>45943</v>
+        <v>46139</v>
       </c>
       <c r="AT7" s="4">
         <f t="shared" si="1"/>
-        <v>45944</v>
+        <v>46140</v>
       </c>
       <c r="AU7" s="4">
-        <f t="shared" ref="AU7" si="2">AT7+1</f>
-        <v>45945</v>
+        <f t="shared" si="1"/>
+        <v>46141</v>
       </c>
       <c r="AV7" s="4">
-        <f t="shared" ref="AV7" si="3">AU7+1</f>
-        <v>45946</v>
+        <f t="shared" si="1"/>
+        <v>46142</v>
       </c>
       <c r="AW7" s="4">
-        <f t="shared" ref="AW7" si="4">AV7+1</f>
-        <v>45947</v>
+        <f t="shared" si="1"/>
+        <v>46143</v>
       </c>
       <c r="AX7" s="4">
-        <f t="shared" ref="AX7" si="5">AW7+1</f>
-        <v>45948</v>
+        <f t="shared" si="1"/>
+        <v>46144</v>
       </c>
       <c r="AY7" s="4">
-        <f t="shared" ref="AY7" si="6">AX7+1</f>
-        <v>45949</v>
+        <f t="shared" si="1"/>
+        <v>46145</v>
       </c>
       <c r="AZ7" s="4">
-        <f t="shared" ref="AZ7" si="7">AY7+1</f>
-        <v>45950</v>
+        <f t="shared" si="1"/>
+        <v>46146</v>
       </c>
       <c r="BA7" s="4">
-        <f t="shared" ref="BA7" si="8">AZ7+1</f>
-        <v>45951</v>
+        <f t="shared" si="1"/>
+        <v>46147</v>
       </c>
       <c r="BB7" s="4">
-        <f t="shared" ref="BB7" si="9">BA7+1</f>
-        <v>45952</v>
+        <f t="shared" si="1"/>
+        <v>46148</v>
       </c>
       <c r="BC7" s="4">
-        <f t="shared" ref="BC7" si="10">BB7+1</f>
-        <v>45953</v>
+        <f t="shared" si="1"/>
+        <v>46149</v>
       </c>
       <c r="BD7" s="4">
-        <f t="shared" ref="BD7" si="11">BC7+1</f>
-        <v>45954</v>
+        <f t="shared" si="1"/>
+        <v>46150</v>
       </c>
       <c r="BE7" s="4">
-        <f t="shared" ref="BE7" si="12">BD7+1</f>
-        <v>45955</v>
+        <f t="shared" si="1"/>
+        <v>46151</v>
       </c>
       <c r="BF7" s="4">
-        <f t="shared" ref="BF7" si="13">BE7+1</f>
-        <v>45956</v>
+        <f t="shared" si="1"/>
+        <v>46152</v>
       </c>
       <c r="BG7" s="4">
-        <f t="shared" ref="BG7" si="14">BF7+1</f>
-        <v>45957</v>
+        <f t="shared" si="1"/>
+        <v>46153</v>
       </c>
       <c r="BH7" s="4">
-        <f t="shared" ref="BH7" si="15">BG7+1</f>
-        <v>45958</v>
-      </c>
-    </row>
-    <row r="8" spans="1:60" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:60" s="15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>26</v>
@@ -4387,7 +4260,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1</v>
+        <v>212</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>3</v>
@@ -4396,13 +4269,13 @@
         <v>4</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>3</v>
@@ -4411,197 +4284,197 @@
         <v>4</v>
       </c>
       <c r="M8" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="O8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="Q8" s="2" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="S8" s="2" t="str">
         <f>UPPER(LEFT(TEXT(S7,"ddd"),1))</f>
         <v>M</v>
       </c>
       <c r="T8" s="2" t="str">
-        <f t="shared" ref="T8:AT8" si="16">UPPER(LEFT(TEXT(T7,"ddd"),1))</f>
+        <f t="shared" ref="T8:BH8" si="2">UPPER(LEFT(TEXT(T7,"ddd"),1))</f>
         <v>J</v>
       </c>
       <c r="U8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>V</v>
       </c>
       <c r="V8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="W8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>D</v>
       </c>
       <c r="X8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="Y8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="Z8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="AA8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>J</v>
       </c>
       <c r="AB8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>V</v>
       </c>
       <c r="AC8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="AD8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>D</v>
       </c>
       <c r="AE8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="AF8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="AG8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="AH8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>J</v>
       </c>
       <c r="AI8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>V</v>
       </c>
       <c r="AJ8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="AK8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>D</v>
       </c>
       <c r="AL8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="AM8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="AN8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="AO8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>J</v>
       </c>
       <c r="AP8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>V</v>
       </c>
       <c r="AQ8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="AR8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>D</v>
       </c>
       <c r="AS8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="AT8" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="AU8" s="2" t="str">
-        <f t="shared" ref="AU8:BA8" si="17">UPPER(LEFT(TEXT(AU7,"ddd"),1))</f>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="AV8" s="2" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="2"/>
         <v>J</v>
       </c>
       <c r="AW8" s="2" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="2"/>
         <v>V</v>
       </c>
       <c r="AX8" s="2" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="AY8" s="2" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="2"/>
         <v>D</v>
       </c>
       <c r="AZ8" s="2" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="BA8" s="2" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="BB8" s="2" t="str">
-        <f t="shared" ref="BB8:BH8" si="18">UPPER(LEFT(TEXT(BB7,"ddd"),1))</f>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="BC8" s="2" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>J</v>
       </c>
       <c r="BD8" s="2" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>V</v>
       </c>
       <c r="BE8" s="2" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="BF8" s="2" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>D</v>
       </c>
       <c r="BG8" s="2" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="BH8" s="2" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
     </row>
-    <row r="9" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="7" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="13"/>
@@ -4615,7 +4488,9 @@
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
+      <c r="P9" s="8" t="s">
+        <v>151</v>
+      </c>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
       <c r="S9" s="8"/>
@@ -4661,7 +4536,7 @@
       <c r="BG9" s="8"/>
       <c r="BH9" s="8"/>
     </row>
-    <row r="10" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>1</v>
       </c>
@@ -4669,38 +4544,39 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>136</v>
+        <v>206</v>
       </c>
       <c r="D10" s="14">
         <v>0</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" s="10">
-        <v>45891</v>
+        <v>46113</v>
       </c>
       <c r="G10" s="10">
-        <v>45892</v>
+        <v>46116</v>
       </c>
       <c r="H10" s="13">
-        <v>1</v>
+        <f>G10-F10</f>
+        <v>3</v>
       </c>
       <c r="I10" s="13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J10" t="s">
-        <v>40</v>
+        <v>161</v>
       </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" t="s">
-        <v>41</v>
+        <v>193</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
@@ -4747,7 +4623,7 @@
       <c r="BG10" s="8"/>
       <c r="BH10" s="8"/>
     </row>
-    <row r="11" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>2</v>
       </c>
@@ -4755,7 +4631,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="D11" s="14">
         <v>0</v>
@@ -4764,29 +4640,30 @@
         <v>9</v>
       </c>
       <c r="F11" s="10">
-        <v>45893</v>
+        <v>46117</v>
       </c>
       <c r="G11" s="10">
-        <v>45894</v>
+        <v>46127</v>
       </c>
       <c r="H11" s="13">
-        <v>1</v>
+        <f t="shared" ref="H11:H33" si="3">G11-F11</f>
+        <v>10</v>
       </c>
       <c r="I11" s="13">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>38</v>
+        <v>161</v>
       </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
       <c r="O11" s="8" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
@@ -4833,7 +4710,7 @@
       <c r="BG11" s="8"/>
       <c r="BH11" s="8"/>
     </row>
-    <row r="12" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>3</v>
       </c>
@@ -4841,38 +4718,36 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="D12" s="14">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F12" s="10">
-        <v>45895</v>
+        <v>46113</v>
       </c>
       <c r="G12" s="10">
-        <v>45901</v>
+        <v>46116</v>
       </c>
       <c r="H12" s="13">
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
       <c r="I12" s="13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J12" t="s">
-        <v>48</v>
+        <v>161</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
-      <c r="O12" t="s">
-        <v>49</v>
-      </c>
       <c r="P12" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
@@ -4919,7 +4794,7 @@
       <c r="BG12" s="8"/>
       <c r="BH12" s="8"/>
     </row>
-    <row r="13" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>4</v>
       </c>
@@ -4927,7 +4802,7 @@
         <v>8</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="D13" s="14">
         <v>0</v>
@@ -4936,29 +4811,30 @@
         <v>9</v>
       </c>
       <c r="F13" s="10">
-        <v>45902</v>
+        <v>46117</v>
       </c>
       <c r="G13" s="10">
-        <v>45904</v>
+        <v>46127</v>
       </c>
       <c r="H13" s="13">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="I13" s="13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>52</v>
+        <v>184</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
       <c r="O13" s="8" t="s">
-        <v>53</v>
+        <v>155</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
@@ -5005,46 +4881,47 @@
       <c r="BG13" s="8"/>
       <c r="BH13" s="8"/>
     </row>
-    <row r="14" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>5</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>197</v>
       </c>
       <c r="D14" s="14">
         <v>0</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="F14" s="10">
-        <v>45905</v>
+        <v>46122</v>
       </c>
       <c r="G14" s="10">
-        <v>45906</v>
+        <v>46125</v>
       </c>
       <c r="H14" s="13">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
       <c r="I14" s="13">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J14" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
       <c r="O14" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
@@ -5091,26 +4968,47 @@
       <c r="BG14" s="8"/>
       <c r="BH14" s="8"/>
     </row>
-    <row r="15" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
+    <row r="15" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>6</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D15" s="14">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="10">
+        <v>46122</v>
+      </c>
+      <c r="G15" s="10">
+        <v>46127</v>
+      </c>
+      <c r="H15" s="13">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="I15" s="13">
+        <v>14</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>182</v>
+      </c>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
+      <c r="O15" s="8" t="s">
+        <v>157</v>
+      </c>
       <c r="P15" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
@@ -5157,46 +5055,47 @@
       <c r="BG15" s="8"/>
       <c r="BH15" s="8"/>
     </row>
-    <row r="16" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>199</v>
       </c>
       <c r="D16" s="14">
         <v>0</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="F16" s="10">
-        <v>45907</v>
+        <v>46128</v>
       </c>
       <c r="G16" s="10">
-        <v>45910</v>
+        <v>46139</v>
       </c>
       <c r="H16" s="13">
-        <v>1</v>
+        <f>G16-F16</f>
+        <v>11</v>
       </c>
       <c r="I16" s="13">
-        <v>6</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>42</v>
+        <v>16</v>
+      </c>
+      <c r="J16" t="s">
+        <v>183</v>
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
       <c r="O16" t="s">
-        <v>61</v>
+        <v>158</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
@@ -5243,49 +5142,43 @@
       <c r="BG16" s="8"/>
       <c r="BH16" s="8"/>
     </row>
-    <row r="17" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="13">
-        <v>7</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>67</v>
+    <row r="17" spans="1:60" s="25" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18" t="s">
+        <v>164</v>
       </c>
       <c r="D17" s="14">
+        <f>AVERAGE(D10:D16)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="10">
-        <v>45911</v>
-      </c>
-      <c r="G17" s="10">
-        <v>45917</v>
-      </c>
-      <c r="H17" s="13">
-        <v>3</v>
-      </c>
-      <c r="I17" s="13">
-        <v>20</v>
-      </c>
-      <c r="J17" t="s">
-        <v>68</v>
-      </c>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8" t="s">
-        <v>70</v>
+      <c r="E17" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="20">
+        <v>46113</v>
+      </c>
+      <c r="G17" s="20">
+        <v>46139</v>
+      </c>
+      <c r="H17" s="19">
+        <f>G17-F17</f>
+        <v>26</v>
+      </c>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18" t="s">
+        <v>165</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
+        <v>151</v>
+      </c>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18"/>
       <c r="S17" s="8"/>
       <c r="T17" s="8"/>
       <c r="U17" s="8"/>
@@ -5329,46 +5222,26 @@
       <c r="BG17" s="8"/>
       <c r="BH17" s="8"/>
     </row>
-    <row r="18" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="13">
-        <v>8</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" s="14">
-        <v>0</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="10">
-        <v>45918</v>
-      </c>
-      <c r="G18" s="10">
-        <v>45918</v>
-      </c>
-      <c r="H18" s="13">
-        <v>1</v>
-      </c>
-      <c r="I18" s="13">
-        <v>8</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>66</v>
-      </c>
+    <row r="18" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D18" s="14"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
-      <c r="O18" t="s">
-        <v>81</v>
-      </c>
+      <c r="O18" s="8"/>
       <c r="P18" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
@@ -5415,46 +5288,44 @@
       <c r="BG18" s="8"/>
       <c r="BH18" s="8"/>
     </row>
-    <row r="19" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>63</v>
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>166</v>
       </c>
       <c r="D19" s="14">
         <v>0</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="F19" s="10">
-        <v>45911</v>
+        <v>46142</v>
       </c>
       <c r="G19" s="10">
-        <v>45912</v>
+        <v>46146</v>
       </c>
       <c r="H19" s="13">
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="I19" s="13">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>64</v>
+        <v>185</v>
       </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
-      <c r="O19" s="8" t="s">
-        <v>65</v>
-      </c>
       <c r="P19" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
@@ -5501,15 +5372,15 @@
       <c r="BG19" s="8"/>
       <c r="BH19" s="8"/>
     </row>
-    <row r="20" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="D20" s="14">
         <v>0</v>
@@ -5518,29 +5389,30 @@
         <v>57</v>
       </c>
       <c r="F20" s="10">
-        <v>45913</v>
+        <v>46121</v>
       </c>
       <c r="G20" s="10">
-        <v>45914</v>
+        <v>46125</v>
       </c>
       <c r="H20" s="13">
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="I20" s="13">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>73</v>
+        <v>186</v>
       </c>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
       <c r="O20" s="8" t="s">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
@@ -5587,15 +5459,15 @@
       <c r="BG20" s="8"/>
       <c r="BH20" s="8"/>
     </row>
-    <row r="21" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="D21" s="14">
         <v>0</v>
@@ -5604,29 +5476,27 @@
         <v>10</v>
       </c>
       <c r="F21" s="10">
-        <v>45915</v>
+        <v>46148</v>
       </c>
       <c r="G21" s="10">
-        <v>45916</v>
+        <v>46153</v>
       </c>
       <c r="H21" s="13">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="I21" s="13">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>77</v>
+        <v>187</v>
       </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
-      <c r="O21" t="s">
-        <v>78</v>
-      </c>
       <c r="P21" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
@@ -5673,26 +5543,47 @@
       <c r="BG21" s="8"/>
       <c r="BH21" s="8"/>
     </row>
-    <row r="22" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
+    <row r="22" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>11</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D22" s="14">
+        <v>0</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="10">
+        <v>46148</v>
+      </c>
+      <c r="G22" s="10">
+        <v>46155</v>
+      </c>
+      <c r="H22" s="13">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="I22" s="13">
+        <v>22</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>185</v>
+      </c>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
+      <c r="O22" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="P22" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
@@ -5739,15 +5630,15 @@
       <c r="BG22" s="8"/>
       <c r="BH22" s="8"/>
     </row>
-    <row r="23" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
         <v>12</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="D23" s="14">
         <v>0</v>
@@ -5756,29 +5647,30 @@
         <v>9</v>
       </c>
       <c r="F23" s="10">
-        <v>45919</v>
+        <v>46156</v>
       </c>
       <c r="G23" s="10">
-        <v>45922</v>
+        <v>46159</v>
       </c>
       <c r="H23" s="13">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
       <c r="I23" s="13">
-        <v>8</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>84</v>
+        <v>10</v>
+      </c>
+      <c r="J23" t="s">
+        <v>161</v>
       </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
       <c r="O23" s="8" t="s">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="P23" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
@@ -5825,46 +5717,47 @@
       <c r="BG23" s="8"/>
       <c r="BH23" s="8"/>
     </row>
-    <row r="24" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
         <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>16</v>
+        <v>146</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>204</v>
       </c>
       <c r="D24" s="14">
         <v>0</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="F24" s="10">
-        <v>45923</v>
+        <v>46160</v>
       </c>
       <c r="G24" s="10">
-        <v>45924</v>
+        <v>46167</v>
       </c>
       <c r="H24" s="13">
-        <v>1</v>
+        <f>G24-F24</f>
+        <v>7</v>
       </c>
       <c r="I24" s="13">
-        <v>6</v>
-      </c>
-      <c r="J24" t="s">
-        <v>82</v>
+        <v>20</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>188</v>
       </c>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" t="s">
-        <v>88</v>
-      </c>
-      <c r="P24" s="8" t="s">
-        <v>163</v>
+        <v>170</v>
+      </c>
+      <c r="P24" t="s">
+        <v>151</v>
       </c>
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
@@ -5911,47 +5804,43 @@
       <c r="BG24" s="8"/>
       <c r="BH24" s="8"/>
     </row>
-    <row r="25" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="13">
-        <v>14</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>153</v>
+    <row r="25" spans="1:60" s="25" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18" t="s">
+        <v>171</v>
       </c>
       <c r="D25" s="14">
+        <f>AVERAGE(D19:D24)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="10">
-        <v>45903</v>
-      </c>
-      <c r="G25" s="10">
-        <v>45908</v>
-      </c>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13">
-        <v>6</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8" t="s">
-        <v>154</v>
+      <c r="F25" s="20">
+        <v>46139</v>
+      </c>
+      <c r="G25" s="20">
+        <v>46174</v>
+      </c>
+      <c r="H25" s="19">
+        <f>G25-F25</f>
+        <v>35</v>
+      </c>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18" t="s">
+        <v>180</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
+        <v>151</v>
+      </c>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="18"/>
       <c r="S25" s="8"/>
       <c r="T25" s="8"/>
       <c r="U25" s="8"/>
@@ -5995,46 +5884,26 @@
       <c r="BG25" s="8"/>
       <c r="BH25" s="8"/>
     </row>
-    <row r="26" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="13">
-        <v>15</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" s="14">
-        <v>0</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="10">
-        <v>45925</v>
-      </c>
-      <c r="G26" s="10">
-        <v>45925</v>
-      </c>
-      <c r="H26" s="13">
-        <v>1</v>
-      </c>
-      <c r="I26" s="13">
-        <v>8</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>91</v>
-      </c>
+    <row r="26" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D26" s="14"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
-      <c r="O26" s="8" t="s">
-        <v>93</v>
-      </c>
+      <c r="O26" s="8"/>
       <c r="P26" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q26" s="8"/>
       <c r="R26" s="8"/>
@@ -6081,15 +5950,15 @@
       <c r="BG26" s="8"/>
       <c r="BH26" s="8"/>
     </row>
-    <row r="27" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>95</v>
+        <v>172</v>
       </c>
       <c r="D27" s="14">
         <v>0</v>
@@ -6098,29 +5967,30 @@
         <v>57</v>
       </c>
       <c r="F27" s="10">
-        <v>45926</v>
+        <v>46175</v>
       </c>
       <c r="G27" s="10">
-        <v>45927</v>
+        <v>46180</v>
       </c>
       <c r="H27" s="13">
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="I27" s="13">
         <v>12</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
       <c r="O27" s="8" t="s">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
@@ -6167,46 +6037,47 @@
       <c r="BG27" s="8"/>
       <c r="BH27" s="8"/>
     </row>
-    <row r="28" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>150</v>
+        <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>207</v>
       </c>
       <c r="D28" s="14">
         <v>0</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="F28" s="10">
-        <v>45931</v>
+        <v>46179</v>
       </c>
       <c r="G28" s="10">
-        <v>45931</v>
+        <v>46188</v>
       </c>
       <c r="H28" s="13">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="I28" s="13">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J28" t="s">
-        <v>94</v>
+        <v>189</v>
       </c>
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
       <c r="M28" s="8"/>
       <c r="N28" s="8"/>
       <c r="O28" t="s">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
@@ -6253,46 +6124,47 @@
       <c r="BG28" s="8"/>
       <c r="BH28" s="8"/>
     </row>
-    <row r="29" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>151</v>
+        <v>17</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="D29" s="14">
         <v>0</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="F29" s="10">
-        <v>45932</v>
+        <v>46189</v>
       </c>
       <c r="G29" s="10">
-        <v>45932</v>
+        <v>46193</v>
       </c>
       <c r="H29" s="13">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="I29" s="13">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
       <c r="N29" s="8"/>
       <c r="O29" s="8" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q29" s="8"/>
       <c r="R29" s="8"/>
@@ -6339,46 +6211,47 @@
       <c r="BG29" s="8"/>
       <c r="BH29" s="8"/>
     </row>
-    <row r="30" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="D30" s="14">
         <v>0</v>
       </c>
       <c r="E30" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="10">
+        <v>46179</v>
+      </c>
+      <c r="G30" s="10">
+        <v>46188</v>
+      </c>
+      <c r="H30" s="13">
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="F30" s="10">
-        <v>45933</v>
-      </c>
-      <c r="G30" s="10">
-        <v>45933</v>
-      </c>
-      <c r="H30" s="13">
-        <v>1</v>
-      </c>
       <c r="I30" s="13">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
-      <c r="O30" s="8" t="s">
-        <v>107</v>
+      <c r="O30" t="s">
+        <v>175</v>
       </c>
       <c r="P30" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
@@ -6425,26 +6298,47 @@
       <c r="BG30" s="8"/>
       <c r="BH30" s="8"/>
     </row>
-    <row r="31" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="8"/>
+    <row r="31" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="13">
+        <v>18</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D31" s="14">
+        <v>0</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="10">
+        <v>46185</v>
+      </c>
+      <c r="G31" s="10">
+        <v>46198</v>
+      </c>
+      <c r="H31" s="13">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="I31" s="13">
+        <v>20</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>191</v>
+      </c>
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
+      <c r="O31" s="8" t="s">
+        <v>176</v>
+      </c>
       <c r="P31" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q31" s="8"/>
       <c r="R31" s="8"/>
@@ -6491,46 +6385,47 @@
       <c r="BG31" s="8"/>
       <c r="BH31" s="8"/>
     </row>
-    <row r="32" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>211</v>
       </c>
       <c r="D32" s="14">
         <v>0</v>
       </c>
       <c r="E32" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="10">
+        <v>46189</v>
+      </c>
+      <c r="G32" s="10">
+        <v>46202</v>
+      </c>
+      <c r="H32" s="13">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="I32" s="13">
         <v>10</v>
       </c>
-      <c r="F32" s="10">
-        <v>45964</v>
-      </c>
-      <c r="G32" s="10">
-        <v>45966</v>
-      </c>
-      <c r="H32" s="13">
-        <v>3</v>
-      </c>
-      <c r="I32" s="13">
-        <v>20</v>
-      </c>
       <c r="J32" t="s">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
       <c r="M32" s="8"/>
       <c r="N32" s="8"/>
-      <c r="O32" s="8" t="s">
-        <v>111</v>
+      <c r="O32" t="s">
+        <v>177</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
@@ -6577,49 +6472,43 @@
       <c r="BG32" s="8"/>
       <c r="BH32" s="8"/>
     </row>
-    <row r="33" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="13">
-        <v>21</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>113</v>
+    <row r="33" spans="1:60" s="25" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18" t="s">
+        <v>178</v>
       </c>
       <c r="D33" s="14">
+        <f>AVERAGE(D27:D32)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="10">
-        <v>45967</v>
-      </c>
-      <c r="G33" s="10">
-        <v>45967</v>
-      </c>
-      <c r="H33" s="13">
-        <v>1</v>
-      </c>
-      <c r="I33" s="13">
-        <v>8</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" t="s">
-        <v>115</v>
+      <c r="E33" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F33" s="20">
+        <v>46175</v>
+      </c>
+      <c r="G33" s="20">
+        <v>46202</v>
+      </c>
+      <c r="H33" s="19">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18" t="s">
+        <v>179</v>
       </c>
       <c r="P33" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="8"/>
+        <v>151</v>
+      </c>
+      <c r="Q33" s="18"/>
+      <c r="R33" s="18"/>
       <c r="S33" s="8"/>
       <c r="T33" s="8"/>
       <c r="U33" s="8"/>
@@ -6663,3001 +6552,94 @@
       <c r="BG33" s="8"/>
       <c r="BH33" s="8"/>
     </row>
-    <row r="34" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="13">
-        <v>22</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C34" t="s">
-        <v>117</v>
-      </c>
-      <c r="D34" s="14">
-        <v>0</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F34" s="10">
-        <v>45968</v>
-      </c>
-      <c r="G34" s="10">
-        <v>45971</v>
-      </c>
-      <c r="H34" s="13">
-        <v>2</v>
-      </c>
-      <c r="I34" s="13">
-        <v>10</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="P34" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="8"/>
-      <c r="U34" s="8"/>
-      <c r="V34" s="8"/>
-      <c r="W34" s="8"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="8"/>
-      <c r="Z34" s="8"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="8"/>
-      <c r="AF34" s="8"/>
-      <c r="AG34" s="8"/>
-      <c r="AH34" s="8"/>
-      <c r="AI34" s="8"/>
-      <c r="AJ34" s="8"/>
-      <c r="AK34" s="8"/>
-      <c r="AL34" s="8"/>
-      <c r="AM34" s="8"/>
-      <c r="AN34" s="8"/>
-      <c r="AO34" s="8"/>
-      <c r="AP34" s="8"/>
-      <c r="AQ34" s="8"/>
-      <c r="AR34" s="8"/>
-      <c r="AS34" s="8"/>
-      <c r="AT34" s="8"/>
-      <c r="AU34" s="8"/>
-      <c r="AV34" s="8"/>
-      <c r="AW34" s="8"/>
-      <c r="AX34" s="8"/>
-      <c r="AY34" s="8"/>
-      <c r="AZ34" s="8"/>
-      <c r="BA34" s="8"/>
-      <c r="BB34" s="8"/>
-      <c r="BC34" s="8"/>
-      <c r="BD34" s="8"/>
-      <c r="BE34" s="8"/>
-      <c r="BF34" s="8"/>
-      <c r="BG34" s="8"/>
-      <c r="BH34" s="8"/>
-    </row>
-    <row r="35" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="13">
-        <v>23</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D35" s="14">
-        <v>0</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F35" s="10">
-        <v>45973</v>
-      </c>
-      <c r="G35" s="10">
-        <v>45973</v>
-      </c>
-      <c r="H35" s="13">
-        <v>1</v>
-      </c>
-      <c r="I35" s="13">
-        <v>6</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="P35" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q35" s="8"/>
-      <c r="R35" s="8"/>
-      <c r="S35" s="8"/>
-      <c r="T35" s="8"/>
-      <c r="U35" s="8"/>
-      <c r="V35" s="8"/>
-      <c r="W35" s="8"/>
-      <c r="X35" s="8"/>
-      <c r="Y35" s="8"/>
-      <c r="Z35" s="8"/>
-      <c r="AA35" s="8"/>
-      <c r="AB35" s="8"/>
-      <c r="AC35" s="8"/>
-      <c r="AD35" s="8"/>
-      <c r="AE35" s="8"/>
-      <c r="AF35" s="8"/>
-      <c r="AG35" s="8"/>
-      <c r="AH35" s="8"/>
-      <c r="AI35" s="8"/>
-      <c r="AJ35" s="8"/>
-      <c r="AK35" s="8"/>
-      <c r="AL35" s="8"/>
-      <c r="AM35" s="8"/>
-      <c r="AN35" s="8"/>
-      <c r="AO35" s="8"/>
-      <c r="AP35" s="8"/>
-      <c r="AQ35" s="8"/>
-      <c r="AR35" s="8"/>
-      <c r="AS35" s="8"/>
-      <c r="AT35" s="8"/>
-      <c r="AU35" s="8"/>
-      <c r="AV35" s="8"/>
-      <c r="AW35" s="8"/>
-      <c r="AX35" s="8"/>
-      <c r="AY35" s="8"/>
-      <c r="AZ35" s="8"/>
-      <c r="BA35" s="8"/>
-      <c r="BB35" s="8"/>
-      <c r="BC35" s="8"/>
-      <c r="BD35" s="8"/>
-      <c r="BE35" s="8"/>
-      <c r="BF35" s="8"/>
-      <c r="BG35" s="8"/>
-      <c r="BH35" s="8"/>
-    </row>
-    <row r="43" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="AH43" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="44" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="AH44" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="AH45" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="AU6:BA6"/>
-    <mergeCell ref="BB6:BH6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="S6:Y6"/>
-    <mergeCell ref="Z6:AF6"/>
-    <mergeCell ref="AG6:AM6"/>
-    <mergeCell ref="AN6:AT6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="K6:N6"/>
-  </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="D9:D35">
-    <cfRule type="dataBar" priority="4">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1"/>
-        <color theme="6" tint="0.59999389629810485"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1D4EC841-9100-439C-9DB5-98C9D5ACCD5B}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S9:BH35">
-    <cfRule type="expression" dxfId="26" priority="8">
-      <formula>S$7=TODAY()</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="9">
-      <formula>AND(S$7&gt;=$F9,S$7&lt;=((($G9-$F9+1)*$D9)+$F9-1))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="10">
-      <formula>AND(S$7&gt;=$F9,S$7&lt;=$G9)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x14">
-      <controls>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="4097" r:id="rId3" name="Scroll Bar 1">
-              <controlPr defaultSize="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-      </controls>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1D4EC841-9100-439C-9DB5-98C9D5ACCD5B}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:borderColor theme="6" tint="0.59999389629810485"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>D9:D35</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF802CD8-39A9-4ECD-ACA4-4544CF43688C}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:BH49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="3.77734375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="31.88671875" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="1" customWidth="1"/>
-    <col min="6" max="7" width="10.77734375" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" customWidth="1"/>
-    <col min="10" max="10" width="14.77734375" customWidth="1"/>
-    <col min="11" max="14" width="10.33203125" customWidth="1"/>
-    <col min="15" max="16" width="20.77734375" customWidth="1"/>
-    <col min="17" max="18" width="11.77734375" customWidth="1"/>
-    <col min="19" max="60" width="3.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:60" s="15" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:60" s="15" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
-        <v>164</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-    </row>
-    <row r="3" spans="1:60" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-    </row>
-    <row r="4" spans="1:60" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="39" t="s">
-        <v>210</v>
-      </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-    </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3">
-        <f>D7+B6</f>
-        <v>45899</v>
-      </c>
-      <c r="F6" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="K6" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="Q6" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="R6" s="36"/>
-      <c r="S6" s="33">
-        <f>S7</f>
-        <v>45899</v>
-      </c>
-      <c r="T6" s="33"/>
-      <c r="U6" s="33"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33">
-        <f>Z7</f>
-        <v>45906</v>
-      </c>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="33"/>
-      <c r="AE6" s="33"/>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="33">
-        <f>AG7</f>
-        <v>45913</v>
-      </c>
-      <c r="AH6" s="33"/>
-      <c r="AI6" s="33"/>
-      <c r="AJ6" s="33"/>
-      <c r="AK6" s="33"/>
-      <c r="AL6" s="33"/>
-      <c r="AM6" s="33"/>
-      <c r="AN6" s="33">
-        <f>AN7</f>
-        <v>45920</v>
-      </c>
-      <c r="AO6" s="33"/>
-      <c r="AP6" s="33"/>
-      <c r="AQ6" s="33"/>
-      <c r="AR6" s="33"/>
-      <c r="AS6" s="33"/>
-      <c r="AT6" s="33"/>
-      <c r="AU6" s="33">
-        <f>AU7</f>
-        <v>45927</v>
-      </c>
-      <c r="AV6" s="33"/>
-      <c r="AW6" s="33"/>
-      <c r="AX6" s="33"/>
-      <c r="AY6" s="33"/>
-      <c r="AZ6" s="33"/>
-      <c r="BA6" s="33"/>
-      <c r="BB6" s="33">
-        <f>BB7</f>
-        <v>45934</v>
-      </c>
-      <c r="BC6" s="33"/>
-      <c r="BD6" s="33"/>
-      <c r="BE6" s="33"/>
-      <c r="BF6" s="33"/>
-      <c r="BG6" s="33"/>
-      <c r="BH6" s="33"/>
-    </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="B7" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="35">
-        <v>45899</v>
-      </c>
-      <c r="E7" s="35"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="17"/>
-      <c r="S7" s="4">
-        <f>C6</f>
-        <v>45899</v>
-      </c>
-      <c r="T7" s="4">
-        <f>S7+1</f>
-        <v>45900</v>
-      </c>
-      <c r="U7" s="4">
-        <f t="shared" ref="U7:AI7" si="0">T7+1</f>
-        <v>45901</v>
-      </c>
-      <c r="V7" s="4">
-        <f t="shared" si="0"/>
-        <v>45902</v>
-      </c>
-      <c r="W7" s="4">
-        <f t="shared" si="0"/>
-        <v>45903</v>
-      </c>
-      <c r="X7" s="4">
-        <f t="shared" si="0"/>
-        <v>45904</v>
-      </c>
-      <c r="Y7" s="4">
-        <f t="shared" si="0"/>
-        <v>45905</v>
-      </c>
-      <c r="Z7" s="4">
-        <f t="shared" si="0"/>
-        <v>45906</v>
-      </c>
-      <c r="AA7" s="4">
-        <f t="shared" si="0"/>
-        <v>45907</v>
-      </c>
-      <c r="AB7" s="4">
-        <f t="shared" si="0"/>
-        <v>45908</v>
-      </c>
-      <c r="AC7" s="4">
-        <f t="shared" si="0"/>
-        <v>45909</v>
-      </c>
-      <c r="AD7" s="4">
-        <f t="shared" si="0"/>
-        <v>45910</v>
-      </c>
-      <c r="AE7" s="4">
-        <f t="shared" si="0"/>
-        <v>45911</v>
-      </c>
-      <c r="AF7" s="4">
-        <f t="shared" si="0"/>
-        <v>45912</v>
-      </c>
-      <c r="AG7" s="4">
-        <f t="shared" si="0"/>
-        <v>45913</v>
-      </c>
-      <c r="AH7" s="4">
-        <f t="shared" si="0"/>
-        <v>45914</v>
-      </c>
-      <c r="AI7" s="4">
-        <f t="shared" si="0"/>
-        <v>45915</v>
-      </c>
-      <c r="AJ7" s="4">
-        <f>AI7+1</f>
-        <v>45916</v>
-      </c>
-      <c r="AK7" s="4">
-        <f t="shared" ref="AK7:BH7" si="1">AJ7+1</f>
-        <v>45917</v>
-      </c>
-      <c r="AL7" s="4">
-        <f t="shared" si="1"/>
-        <v>45918</v>
-      </c>
-      <c r="AM7" s="4">
-        <f t="shared" si="1"/>
-        <v>45919</v>
-      </c>
-      <c r="AN7" s="4">
-        <f t="shared" si="1"/>
-        <v>45920</v>
-      </c>
-      <c r="AO7" s="4">
-        <f t="shared" si="1"/>
-        <v>45921</v>
-      </c>
-      <c r="AP7" s="4">
-        <f t="shared" si="1"/>
-        <v>45922</v>
-      </c>
-      <c r="AQ7" s="4">
-        <f t="shared" si="1"/>
-        <v>45923</v>
-      </c>
-      <c r="AR7" s="4">
-        <f t="shared" si="1"/>
-        <v>45924</v>
-      </c>
-      <c r="AS7" s="4">
-        <f t="shared" si="1"/>
-        <v>45925</v>
-      </c>
-      <c r="AT7" s="4">
-        <f t="shared" si="1"/>
-        <v>45926</v>
-      </c>
-      <c r="AU7" s="4">
-        <f t="shared" si="1"/>
-        <v>45927</v>
-      </c>
-      <c r="AV7" s="4">
-        <f t="shared" si="1"/>
-        <v>45928</v>
-      </c>
-      <c r="AW7" s="4">
-        <f t="shared" si="1"/>
-        <v>45929</v>
-      </c>
-      <c r="AX7" s="4">
-        <f t="shared" si="1"/>
-        <v>45930</v>
-      </c>
-      <c r="AY7" s="4">
-        <f t="shared" si="1"/>
-        <v>45931</v>
-      </c>
-      <c r="AZ7" s="4">
-        <f t="shared" si="1"/>
-        <v>45932</v>
-      </c>
-      <c r="BA7" s="4">
-        <f t="shared" si="1"/>
-        <v>45933</v>
-      </c>
-      <c r="BB7" s="4">
-        <f t="shared" si="1"/>
-        <v>45934</v>
-      </c>
-      <c r="BC7" s="4">
-        <f t="shared" si="1"/>
-        <v>45935</v>
-      </c>
-      <c r="BD7" s="4">
-        <f t="shared" si="1"/>
-        <v>45936</v>
-      </c>
-      <c r="BE7" s="4">
-        <f t="shared" si="1"/>
-        <v>45937</v>
-      </c>
-      <c r="BF7" s="4">
-        <f t="shared" si="1"/>
-        <v>45938</v>
-      </c>
-      <c r="BG7" s="4">
-        <f t="shared" si="1"/>
-        <v>45939</v>
-      </c>
-      <c r="BH7" s="4">
-        <f t="shared" si="1"/>
-        <v>45940</v>
-      </c>
-    </row>
-    <row r="8" spans="1:60" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="S8" s="2" t="str">
-        <f>UPPER(LEFT(TEXT(S7,"ddd"),1))</f>
-        <v>S</v>
-      </c>
-      <c r="T8" s="2" t="str">
-        <f t="shared" ref="T8:BH8" si="2">UPPER(LEFT(TEXT(T7,"ddd"),1))</f>
-        <v>D</v>
-      </c>
-      <c r="U8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>L</v>
-      </c>
-      <c r="V8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
-      </c>
-      <c r="W8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
-      </c>
-      <c r="X8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>J</v>
-      </c>
-      <c r="Y8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>V</v>
-      </c>
-      <c r="Z8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>S</v>
-      </c>
-      <c r="AA8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>D</v>
-      </c>
-      <c r="AB8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>L</v>
-      </c>
-      <c r="AC8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
-      </c>
-      <c r="AD8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
-      </c>
-      <c r="AE8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>J</v>
-      </c>
-      <c r="AF8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>V</v>
-      </c>
-      <c r="AG8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>S</v>
-      </c>
-      <c r="AH8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>D</v>
-      </c>
-      <c r="AI8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>L</v>
-      </c>
-      <c r="AJ8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
-      </c>
-      <c r="AK8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
-      </c>
-      <c r="AL8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>J</v>
-      </c>
-      <c r="AM8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>V</v>
-      </c>
-      <c r="AN8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>S</v>
-      </c>
-      <c r="AO8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>D</v>
-      </c>
-      <c r="AP8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>L</v>
-      </c>
-      <c r="AQ8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
-      </c>
-      <c r="AR8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
-      </c>
-      <c r="AS8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>J</v>
-      </c>
-      <c r="AT8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>V</v>
-      </c>
-      <c r="AU8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>S</v>
-      </c>
-      <c r="AV8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>D</v>
-      </c>
-      <c r="AW8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>L</v>
-      </c>
-      <c r="AX8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
-      </c>
-      <c r="AY8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
-      </c>
-      <c r="AZ8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>J</v>
-      </c>
-      <c r="BA8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>V</v>
-      </c>
-      <c r="BB8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>S</v>
-      </c>
-      <c r="BC8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>D</v>
-      </c>
-      <c r="BD8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>L</v>
-      </c>
-      <c r="BE8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
-      </c>
-      <c r="BF8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>M</v>
-      </c>
-      <c r="BG8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>J</v>
-      </c>
-      <c r="BH8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>V</v>
-      </c>
-    </row>
-    <row r="9" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="8"/>
-      <c r="AA9" s="8"/>
-      <c r="AB9" s="8"/>
-      <c r="AC9" s="8"/>
-      <c r="AD9" s="8"/>
-      <c r="AE9" s="8"/>
-      <c r="AF9" s="8"/>
-      <c r="AG9" s="8"/>
-      <c r="AH9" s="8"/>
-      <c r="AI9" s="8"/>
-      <c r="AJ9" s="8"/>
-      <c r="AK9" s="8"/>
-      <c r="AL9" s="8"/>
-      <c r="AM9" s="8"/>
-      <c r="AN9" s="8"/>
-      <c r="AO9" s="8"/>
-      <c r="AP9" s="8"/>
-      <c r="AQ9" s="8"/>
-      <c r="AR9" s="8"/>
-      <c r="AS9" s="8"/>
-      <c r="AT9" s="8"/>
-      <c r="AU9" s="8"/>
-      <c r="AV9" s="8"/>
-      <c r="AW9" s="8"/>
-      <c r="AX9" s="8"/>
-      <c r="AY9" s="8"/>
-      <c r="AZ9" s="8"/>
-      <c r="BA9" s="8"/>
-      <c r="BB9" s="8"/>
-      <c r="BC9" s="8"/>
-      <c r="BD9" s="8"/>
-      <c r="BE9" s="8"/>
-      <c r="BF9" s="8"/>
-      <c r="BG9" s="8"/>
-      <c r="BH9" s="8"/>
-    </row>
-    <row r="10" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="13">
-        <v>1</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s">
-        <v>220</v>
-      </c>
-      <c r="D10" s="14">
-        <v>0</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="10">
-        <v>45901</v>
-      </c>
-      <c r="G10" s="10">
-        <v>45904</v>
-      </c>
-      <c r="H10" s="13">
-        <f>G10-F10</f>
-        <v>3</v>
-      </c>
-      <c r="I10" s="13">
-        <v>8</v>
-      </c>
-      <c r="J10" t="s">
-        <v>175</v>
-      </c>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" t="s">
-        <v>207</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="8"/>
-      <c r="AA10" s="8"/>
-      <c r="AB10" s="8"/>
-      <c r="AC10" s="8"/>
-      <c r="AD10" s="8"/>
-      <c r="AE10" s="8"/>
-      <c r="AF10" s="8"/>
-      <c r="AG10" s="8"/>
-      <c r="AH10" s="8"/>
-      <c r="AI10" s="8"/>
-      <c r="AJ10" s="8"/>
-      <c r="AK10" s="8"/>
-      <c r="AL10" s="8"/>
-      <c r="AM10" s="8"/>
-      <c r="AN10" s="8"/>
-      <c r="AO10" s="8"/>
-      <c r="AP10" s="8"/>
-      <c r="AQ10" s="8"/>
-      <c r="AR10" s="8"/>
-      <c r="AS10" s="8"/>
-      <c r="AT10" s="8"/>
-      <c r="AU10" s="8"/>
-      <c r="AV10" s="8"/>
-      <c r="AW10" s="8"/>
-      <c r="AX10" s="8"/>
-      <c r="AY10" s="8"/>
-      <c r="AZ10" s="8"/>
-      <c r="BA10" s="8"/>
-      <c r="BB10" s="8"/>
-      <c r="BC10" s="8"/>
-      <c r="BD10" s="8"/>
-      <c r="BE10" s="8"/>
-      <c r="BF10" s="8"/>
-      <c r="BG10" s="8"/>
-      <c r="BH10" s="8"/>
-    </row>
-    <row r="11" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="13">
-        <v>2</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="D11" s="14">
-        <v>0</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="10">
-        <v>45905</v>
-      </c>
-      <c r="G11" s="10">
-        <v>45915</v>
-      </c>
-      <c r="H11" s="13">
-        <f t="shared" ref="H11:H33" si="3">G11-F11</f>
-        <v>10</v>
-      </c>
-      <c r="I11" s="13">
-        <v>12</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="P11" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
-      <c r="Z11" s="8"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="8"/>
-      <c r="AE11" s="8"/>
-      <c r="AF11" s="8"/>
-      <c r="AG11" s="8"/>
-      <c r="AH11" s="8"/>
-      <c r="AI11" s="8"/>
-      <c r="AJ11" s="8"/>
-      <c r="AK11" s="8"/>
-      <c r="AL11" s="8"/>
-      <c r="AM11" s="8"/>
-      <c r="AN11" s="8"/>
-      <c r="AO11" s="8"/>
-      <c r="AP11" s="8"/>
-      <c r="AQ11" s="8"/>
-      <c r="AR11" s="8"/>
-      <c r="AS11" s="8"/>
-      <c r="AT11" s="8"/>
-      <c r="AU11" s="8"/>
-      <c r="AV11" s="8"/>
-      <c r="AW11" s="8"/>
-      <c r="AX11" s="8"/>
-      <c r="AY11" s="8"/>
-      <c r="AZ11" s="8"/>
-      <c r="BA11" s="8"/>
-      <c r="BB11" s="8"/>
-      <c r="BC11" s="8"/>
-      <c r="BD11" s="8"/>
-      <c r="BE11" s="8"/>
-      <c r="BF11" s="8"/>
-      <c r="BG11" s="8"/>
-      <c r="BH11" s="8"/>
-    </row>
-    <row r="12" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="13">
-        <v>3</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>168</v>
-      </c>
-      <c r="D12" s="14">
-        <v>0</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="10">
-        <v>45901</v>
-      </c>
-      <c r="G12" s="10">
-        <v>45904</v>
-      </c>
-      <c r="H12" s="13">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="I12" s="13">
-        <v>6</v>
-      </c>
-      <c r="J12" t="s">
-        <v>175</v>
-      </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="P12" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="8"/>
-      <c r="AA12" s="8"/>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
-      <c r="AD12" s="8"/>
-      <c r="AE12" s="8"/>
-      <c r="AF12" s="8"/>
-      <c r="AG12" s="8"/>
-      <c r="AH12" s="8"/>
-      <c r="AI12" s="8"/>
-      <c r="AJ12" s="8"/>
-      <c r="AK12" s="8"/>
-      <c r="AL12" s="8"/>
-      <c r="AM12" s="8"/>
-      <c r="AN12" s="8"/>
-      <c r="AO12" s="8"/>
-      <c r="AP12" s="8"/>
-      <c r="AQ12" s="8"/>
-      <c r="AR12" s="8"/>
-      <c r="AS12" s="8"/>
-      <c r="AT12" s="8"/>
-      <c r="AU12" s="8"/>
-      <c r="AV12" s="8"/>
-      <c r="AW12" s="8"/>
-      <c r="AX12" s="8"/>
-      <c r="AY12" s="8"/>
-      <c r="AZ12" s="8"/>
-      <c r="BA12" s="8"/>
-      <c r="BB12" s="8"/>
-      <c r="BC12" s="8"/>
-      <c r="BD12" s="8"/>
-      <c r="BE12" s="8"/>
-      <c r="BF12" s="8"/>
-      <c r="BG12" s="8"/>
-      <c r="BH12" s="8"/>
-    </row>
-    <row r="13" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="13">
-        <v>4</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="D13" s="14">
-        <v>0</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="10">
-        <v>45905</v>
-      </c>
-      <c r="G13" s="10">
-        <v>45915</v>
-      </c>
-      <c r="H13" s="13">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="I13" s="13">
-        <v>10</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="8"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="8"/>
-      <c r="AF13" s="8"/>
-      <c r="AG13" s="8"/>
-      <c r="AH13" s="8"/>
-      <c r="AI13" s="8"/>
-      <c r="AJ13" s="8"/>
-      <c r="AK13" s="8"/>
-      <c r="AL13" s="8"/>
-      <c r="AM13" s="8"/>
-      <c r="AN13" s="8"/>
-      <c r="AO13" s="8"/>
-      <c r="AP13" s="8"/>
-      <c r="AQ13" s="8"/>
-      <c r="AR13" s="8"/>
-      <c r="AS13" s="8"/>
-      <c r="AT13" s="8"/>
-      <c r="AU13" s="8"/>
-      <c r="AV13" s="8"/>
-      <c r="AW13" s="8"/>
-      <c r="AX13" s="8"/>
-      <c r="AY13" s="8"/>
-      <c r="AZ13" s="8"/>
-      <c r="BA13" s="8"/>
-      <c r="BB13" s="8"/>
-      <c r="BC13" s="8"/>
-      <c r="BD13" s="8"/>
-      <c r="BE13" s="8"/>
-      <c r="BF13" s="8"/>
-      <c r="BG13" s="8"/>
-      <c r="BH13" s="8"/>
-    </row>
-    <row r="14" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="13">
-        <v>5</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="C14" t="s">
-        <v>211</v>
-      </c>
-      <c r="D14" s="14">
-        <v>0</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="10">
-        <v>45910</v>
-      </c>
-      <c r="G14" s="10">
-        <v>45913</v>
-      </c>
-      <c r="H14" s="13">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="I14" s="13">
-        <v>12</v>
-      </c>
-      <c r="J14" t="s">
-        <v>175</v>
-      </c>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" t="s">
-        <v>170</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="8"/>
-      <c r="AA14" s="8"/>
-      <c r="AB14" s="8"/>
-      <c r="AC14" s="8"/>
-      <c r="AD14" s="8"/>
-      <c r="AE14" s="8"/>
-      <c r="AF14" s="8"/>
-      <c r="AG14" s="8"/>
-      <c r="AH14" s="8"/>
-      <c r="AI14" s="8"/>
-      <c r="AJ14" s="8"/>
-      <c r="AK14" s="8"/>
-      <c r="AL14" s="8"/>
-      <c r="AM14" s="8"/>
-      <c r="AN14" s="8"/>
-      <c r="AO14" s="8"/>
-      <c r="AP14" s="8"/>
-      <c r="AQ14" s="8"/>
-      <c r="AR14" s="8"/>
-      <c r="AS14" s="8"/>
-      <c r="AT14" s="8"/>
-      <c r="AU14" s="8"/>
-      <c r="AV14" s="8"/>
-      <c r="AW14" s="8"/>
-      <c r="AX14" s="8"/>
-      <c r="AY14" s="8"/>
-      <c r="AZ14" s="8"/>
-      <c r="BA14" s="8"/>
-      <c r="BB14" s="8"/>
-      <c r="BC14" s="8"/>
-      <c r="BD14" s="8"/>
-      <c r="BE14" s="8"/>
-      <c r="BF14" s="8"/>
-      <c r="BG14" s="8"/>
-      <c r="BH14" s="8"/>
-    </row>
-    <row r="15" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="13">
-        <v>6</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D15" s="14">
-        <v>0</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="10">
-        <v>45910</v>
-      </c>
-      <c r="G15" s="10">
-        <v>45915</v>
-      </c>
-      <c r="H15" s="13">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="I15" s="13">
-        <v>14</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="P15" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="8"/>
-      <c r="AA15" s="8"/>
-      <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
-      <c r="AD15" s="8"/>
-      <c r="AE15" s="8"/>
-      <c r="AF15" s="8"/>
-      <c r="AG15" s="8"/>
-      <c r="AH15" s="8"/>
-      <c r="AI15" s="8"/>
-      <c r="AJ15" s="8"/>
-      <c r="AK15" s="8"/>
-      <c r="AL15" s="8"/>
-      <c r="AM15" s="8"/>
-      <c r="AN15" s="8"/>
-      <c r="AO15" s="8"/>
-      <c r="AP15" s="8"/>
-      <c r="AQ15" s="8"/>
-      <c r="AR15" s="8"/>
-      <c r="AS15" s="8"/>
-      <c r="AT15" s="8"/>
-      <c r="AU15" s="8"/>
-      <c r="AV15" s="8"/>
-      <c r="AW15" s="8"/>
-      <c r="AX15" s="8"/>
-      <c r="AY15" s="8"/>
-      <c r="AZ15" s="8"/>
-      <c r="BA15" s="8"/>
-      <c r="BB15" s="8"/>
-      <c r="BC15" s="8"/>
-      <c r="BD15" s="8"/>
-      <c r="BE15" s="8"/>
-      <c r="BF15" s="8"/>
-      <c r="BG15" s="8"/>
-      <c r="BH15" s="8"/>
-    </row>
-    <row r="16" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="13">
-        <v>7</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="C16" t="s">
-        <v>213</v>
-      </c>
-      <c r="D16" s="14">
-        <v>0</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="10">
-        <v>45916</v>
-      </c>
-      <c r="G16" s="10">
-        <v>45920</v>
-      </c>
-      <c r="H16" s="13">
-        <f>G16-F16</f>
-        <v>4</v>
-      </c>
-      <c r="I16" s="13">
-        <v>16</v>
-      </c>
-      <c r="J16" t="s">
-        <v>197</v>
-      </c>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" t="s">
-        <v>172</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="8"/>
-      <c r="AA16" s="8"/>
-      <c r="AB16" s="8"/>
-      <c r="AC16" s="8"/>
-      <c r="AD16" s="8"/>
-      <c r="AE16" s="8"/>
-      <c r="AF16" s="8"/>
-      <c r="AG16" s="8"/>
-      <c r="AH16" s="8"/>
-      <c r="AI16" s="8"/>
-      <c r="AJ16" s="8"/>
-      <c r="AK16" s="8"/>
-      <c r="AL16" s="8"/>
-      <c r="AM16" s="8"/>
-      <c r="AN16" s="8"/>
-      <c r="AO16" s="8"/>
-      <c r="AP16" s="8"/>
-      <c r="AQ16" s="8"/>
-      <c r="AR16" s="8"/>
-      <c r="AS16" s="8"/>
-      <c r="AT16" s="8"/>
-      <c r="AU16" s="8"/>
-      <c r="AV16" s="8"/>
-      <c r="AW16" s="8"/>
-      <c r="AX16" s="8"/>
-      <c r="AY16" s="8"/>
-      <c r="AZ16" s="8"/>
-      <c r="BA16" s="8"/>
-      <c r="BB16" s="8"/>
-      <c r="BC16" s="8"/>
-      <c r="BD16" s="8"/>
-      <c r="BE16" s="8"/>
-      <c r="BF16" s="8"/>
-      <c r="BG16" s="8"/>
-      <c r="BH16" s="8"/>
-    </row>
-    <row r="17" spans="1:60" s="28" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D17" s="14">
-        <f>AVERAGE(D10:D16)</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="23">
-        <v>45901</v>
-      </c>
-      <c r="G17" s="23">
-        <v>45922</v>
-      </c>
-      <c r="H17" s="22">
-        <f>G17-F17</f>
-        <v>21</v>
-      </c>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
-      <c r="Z17" s="8"/>
-      <c r="AA17" s="8"/>
-      <c r="AB17" s="8"/>
-      <c r="AC17" s="8"/>
-      <c r="AD17" s="8"/>
-      <c r="AE17" s="8"/>
-      <c r="AF17" s="8"/>
-      <c r="AG17" s="8"/>
-      <c r="AH17" s="8"/>
-      <c r="AI17" s="8"/>
-      <c r="AJ17" s="8"/>
-      <c r="AK17" s="8"/>
-      <c r="AL17" s="8"/>
-      <c r="AM17" s="8"/>
-      <c r="AN17" s="8"/>
-      <c r="AO17" s="8"/>
-      <c r="AP17" s="8"/>
-      <c r="AQ17" s="8"/>
-      <c r="AR17" s="8"/>
-      <c r="AS17" s="8"/>
-      <c r="AT17" s="8"/>
-      <c r="AU17" s="8"/>
-      <c r="AV17" s="8"/>
-      <c r="AW17" s="8"/>
-      <c r="AX17" s="8"/>
-      <c r="AY17" s="8"/>
-      <c r="AZ17" s="8"/>
-      <c r="BA17" s="8"/>
-      <c r="BB17" s="8"/>
-      <c r="BC17" s="8"/>
-      <c r="BD17" s="8"/>
-      <c r="BE17" s="8"/>
-      <c r="BF17" s="8"/>
-      <c r="BG17" s="8"/>
-      <c r="BH17" s="8"/>
-    </row>
-    <row r="18" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="8"/>
-      <c r="AA18" s="8"/>
-      <c r="AB18" s="8"/>
-      <c r="AC18" s="8"/>
-      <c r="AD18" s="8"/>
-      <c r="AE18" s="8"/>
-      <c r="AF18" s="8"/>
-      <c r="AG18" s="8"/>
-      <c r="AH18" s="8"/>
-      <c r="AI18" s="8"/>
-      <c r="AJ18" s="8"/>
-      <c r="AK18" s="8"/>
-      <c r="AL18" s="8"/>
-      <c r="AM18" s="8"/>
-      <c r="AN18" s="8"/>
-      <c r="AO18" s="8"/>
-      <c r="AP18" s="8"/>
-      <c r="AQ18" s="8"/>
-      <c r="AR18" s="8"/>
-      <c r="AS18" s="8"/>
-      <c r="AT18" s="8"/>
-      <c r="AU18" s="8"/>
-      <c r="AV18" s="8"/>
-      <c r="AW18" s="8"/>
-      <c r="AX18" s="8"/>
-      <c r="AY18" s="8"/>
-      <c r="AZ18" s="8"/>
-      <c r="BA18" s="8"/>
-      <c r="BB18" s="8"/>
-      <c r="BC18" s="8"/>
-      <c r="BD18" s="8"/>
-      <c r="BE18" s="8"/>
-      <c r="BF18" s="8"/>
-      <c r="BG18" s="8"/>
-      <c r="BH18" s="8"/>
-    </row>
-    <row r="19" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="13">
-        <v>8</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" t="s">
-        <v>180</v>
-      </c>
-      <c r="D19" s="14">
-        <v>0</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="10">
-        <v>45921</v>
-      </c>
-      <c r="G19" s="10">
-        <v>45925</v>
-      </c>
-      <c r="H19" s="13">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="I19" s="13">
-        <v>14</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="P19" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
-      <c r="X19" s="8"/>
-      <c r="Y19" s="8"/>
-      <c r="Z19" s="8"/>
-      <c r="AA19" s="8"/>
-      <c r="AB19" s="8"/>
-      <c r="AC19" s="8"/>
-      <c r="AD19" s="8"/>
-      <c r="AE19" s="8"/>
-      <c r="AF19" s="8"/>
-      <c r="AG19" s="8"/>
-      <c r="AH19" s="8"/>
-      <c r="AI19" s="8"/>
-      <c r="AJ19" s="8"/>
-      <c r="AK19" s="8"/>
-      <c r="AL19" s="8"/>
-      <c r="AM19" s="8"/>
-      <c r="AN19" s="8"/>
-      <c r="AO19" s="8"/>
-      <c r="AP19" s="8"/>
-      <c r="AQ19" s="8"/>
-      <c r="AR19" s="8"/>
-      <c r="AS19" s="8"/>
-      <c r="AT19" s="8"/>
-      <c r="AU19" s="8"/>
-      <c r="AV19" s="8"/>
-      <c r="AW19" s="8"/>
-      <c r="AX19" s="8"/>
-      <c r="AY19" s="8"/>
-      <c r="AZ19" s="8"/>
-      <c r="BA19" s="8"/>
-      <c r="BB19" s="8"/>
-      <c r="BC19" s="8"/>
-      <c r="BD19" s="8"/>
-      <c r="BE19" s="8"/>
-      <c r="BF19" s="8"/>
-      <c r="BG19" s="8"/>
-      <c r="BH19" s="8"/>
-    </row>
-    <row r="20" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="13">
-        <v>9</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="D20" s="14">
-        <v>0</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F20" s="10">
-        <v>45926</v>
-      </c>
-      <c r="G20" s="10">
-        <v>45930</v>
-      </c>
-      <c r="H20" s="13">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="I20" s="13">
-        <v>18</v>
-      </c>
-      <c r="J20" t="s">
-        <v>200</v>
-      </c>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
-      <c r="V20" s="8"/>
-      <c r="W20" s="8"/>
-      <c r="X20" s="8"/>
-      <c r="Y20" s="8"/>
-      <c r="Z20" s="8"/>
-      <c r="AA20" s="8"/>
-      <c r="AB20" s="8"/>
-      <c r="AC20" s="8"/>
-      <c r="AD20" s="8"/>
-      <c r="AE20" s="8"/>
-      <c r="AF20" s="8"/>
-      <c r="AG20" s="8"/>
-      <c r="AH20" s="8"/>
-      <c r="AI20" s="8"/>
-      <c r="AJ20" s="8"/>
-      <c r="AK20" s="8"/>
-      <c r="AL20" s="8"/>
-      <c r="AM20" s="8"/>
-      <c r="AN20" s="8"/>
-      <c r="AO20" s="8"/>
-      <c r="AP20" s="8"/>
-      <c r="AQ20" s="8"/>
-      <c r="AR20" s="8"/>
-      <c r="AS20" s="8"/>
-      <c r="AT20" s="8"/>
-      <c r="AU20" s="8"/>
-      <c r="AV20" s="8"/>
-      <c r="AW20" s="8"/>
-      <c r="AX20" s="8"/>
-      <c r="AY20" s="8"/>
-      <c r="AZ20" s="8"/>
-      <c r="BA20" s="8"/>
-      <c r="BB20" s="8"/>
-      <c r="BC20" s="8"/>
-      <c r="BD20" s="8"/>
-      <c r="BE20" s="8"/>
-      <c r="BF20" s="8"/>
-      <c r="BG20" s="8"/>
-      <c r="BH20" s="8"/>
-    </row>
-    <row r="21" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="13">
-        <v>10</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" t="s">
-        <v>182</v>
-      </c>
-      <c r="D21" s="14">
-        <v>0</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="10">
-        <v>45931</v>
-      </c>
-      <c r="G21" s="10">
-        <v>45936</v>
-      </c>
-      <c r="H21" s="13">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="I21" s="13">
-        <v>20</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="P21" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="8"/>
-      <c r="S21" s="8"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="8"/>
-      <c r="V21" s="8"/>
-      <c r="W21" s="8"/>
-      <c r="X21" s="8"/>
-      <c r="Y21" s="8"/>
-      <c r="Z21" s="8"/>
-      <c r="AA21" s="8"/>
-      <c r="AB21" s="8"/>
-      <c r="AC21" s="8"/>
-      <c r="AD21" s="8"/>
-      <c r="AE21" s="8"/>
-      <c r="AF21" s="8"/>
-      <c r="AG21" s="8"/>
-      <c r="AH21" s="8"/>
-      <c r="AI21" s="8"/>
-      <c r="AJ21" s="8"/>
-      <c r="AK21" s="8"/>
-      <c r="AL21" s="8"/>
-      <c r="AM21" s="8"/>
-      <c r="AN21" s="8"/>
-      <c r="AO21" s="8"/>
-      <c r="AP21" s="8"/>
-      <c r="AQ21" s="8"/>
-      <c r="AR21" s="8"/>
-      <c r="AS21" s="8"/>
-      <c r="AT21" s="8"/>
-      <c r="AU21" s="8"/>
-      <c r="AV21" s="8"/>
-      <c r="AW21" s="8"/>
-      <c r="AX21" s="8"/>
-      <c r="AY21" s="8"/>
-      <c r="AZ21" s="8"/>
-      <c r="BA21" s="8"/>
-      <c r="BB21" s="8"/>
-      <c r="BC21" s="8"/>
-      <c r="BD21" s="8"/>
-      <c r="BE21" s="8"/>
-      <c r="BF21" s="8"/>
-      <c r="BG21" s="8"/>
-      <c r="BH21" s="8"/>
-    </row>
-    <row r="22" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="13">
-        <v>11</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="D22" s="14">
-        <v>0</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="10">
-        <v>45931</v>
-      </c>
-      <c r="G22" s="10">
-        <v>45938</v>
-      </c>
-      <c r="H22" s="13">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
-      <c r="I22" s="13">
-        <v>22</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="8"/>
-      <c r="W22" s="8"/>
-      <c r="X22" s="8"/>
-      <c r="Y22" s="8"/>
-      <c r="Z22" s="8"/>
-      <c r="AA22" s="8"/>
-      <c r="AB22" s="8"/>
-      <c r="AC22" s="8"/>
-      <c r="AD22" s="8"/>
-      <c r="AE22" s="8"/>
-      <c r="AF22" s="8"/>
-      <c r="AG22" s="8"/>
-      <c r="AH22" s="8"/>
-      <c r="AI22" s="8"/>
-      <c r="AJ22" s="8"/>
-      <c r="AK22" s="8"/>
-      <c r="AL22" s="8"/>
-      <c r="AM22" s="8"/>
-      <c r="AN22" s="8"/>
-      <c r="AO22" s="8"/>
-      <c r="AP22" s="8"/>
-      <c r="AQ22" s="8"/>
-      <c r="AR22" s="8"/>
-      <c r="AS22" s="8"/>
-      <c r="AT22" s="8"/>
-      <c r="AU22" s="8"/>
-      <c r="AV22" s="8"/>
-      <c r="AW22" s="8"/>
-      <c r="AX22" s="8"/>
-      <c r="AY22" s="8"/>
-      <c r="AZ22" s="8"/>
-      <c r="BA22" s="8"/>
-      <c r="BB22" s="8"/>
-      <c r="BC22" s="8"/>
-      <c r="BD22" s="8"/>
-      <c r="BE22" s="8"/>
-      <c r="BF22" s="8"/>
-      <c r="BG22" s="8"/>
-      <c r="BH22" s="8"/>
-    </row>
-    <row r="23" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="13">
-        <v>12</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="D23" s="14">
-        <v>0</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="10">
-        <v>45939</v>
-      </c>
-      <c r="G23" s="10">
-        <v>45942</v>
-      </c>
-      <c r="H23" s="13">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="I23" s="13">
-        <v>10</v>
-      </c>
-      <c r="J23" t="s">
-        <v>175</v>
-      </c>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="8"/>
-      <c r="V23" s="8"/>
-      <c r="W23" s="8"/>
-      <c r="X23" s="8"/>
-      <c r="Y23" s="8"/>
-      <c r="Z23" s="8"/>
-      <c r="AA23" s="8"/>
-      <c r="AB23" s="8"/>
-      <c r="AC23" s="8"/>
-      <c r="AD23" s="8"/>
-      <c r="AE23" s="8"/>
-      <c r="AF23" s="8"/>
-      <c r="AG23" s="8"/>
-      <c r="AH23" s="8"/>
-      <c r="AI23" s="8"/>
-      <c r="AJ23" s="8"/>
-      <c r="AK23" s="8"/>
-      <c r="AL23" s="8"/>
-      <c r="AM23" s="8"/>
-      <c r="AN23" s="8"/>
-      <c r="AO23" s="8"/>
-      <c r="AP23" s="8"/>
-      <c r="AQ23" s="8"/>
-      <c r="AR23" s="8"/>
-      <c r="AS23" s="8"/>
-      <c r="AT23" s="8"/>
-      <c r="AU23" s="8"/>
-      <c r="AV23" s="8"/>
-      <c r="AW23" s="8"/>
-      <c r="AX23" s="8"/>
-      <c r="AY23" s="8"/>
-      <c r="AZ23" s="8"/>
-      <c r="BA23" s="8"/>
-      <c r="BB23" s="8"/>
-      <c r="BC23" s="8"/>
-      <c r="BD23" s="8"/>
-      <c r="BE23" s="8"/>
-      <c r="BF23" s="8"/>
-      <c r="BG23" s="8"/>
-      <c r="BH23" s="8"/>
-    </row>
-    <row r="24" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="13">
-        <v>13</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="C24" t="s">
-        <v>218</v>
-      </c>
-      <c r="D24" s="14">
-        <v>0</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F24" s="10">
-        <v>45943</v>
-      </c>
-      <c r="G24" s="10">
-        <v>45948</v>
-      </c>
-      <c r="H24" s="13">
-        <f>G24-F24</f>
-        <v>5</v>
-      </c>
-      <c r="I24" s="13">
-        <v>20</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" t="s">
-        <v>184</v>
-      </c>
-      <c r="P24" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
-      <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="8"/>
-      <c r="W24" s="8"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="8"/>
-      <c r="Z24" s="8"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
-      <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="8"/>
-      <c r="AF24" s="8"/>
-      <c r="AG24" s="8"/>
-      <c r="AH24" s="8"/>
-      <c r="AI24" s="8"/>
-      <c r="AJ24" s="8"/>
-      <c r="AK24" s="8"/>
-      <c r="AL24" s="8"/>
-      <c r="AM24" s="8"/>
-      <c r="AN24" s="8"/>
-      <c r="AO24" s="8"/>
-      <c r="AP24" s="8"/>
-      <c r="AQ24" s="8"/>
-      <c r="AR24" s="8"/>
-      <c r="AS24" s="8"/>
-      <c r="AT24" s="8"/>
-      <c r="AU24" s="8"/>
-      <c r="AV24" s="8"/>
-      <c r="AW24" s="8"/>
-      <c r="AX24" s="8"/>
-      <c r="AY24" s="8"/>
-      <c r="AZ24" s="8"/>
-      <c r="BA24" s="8"/>
-      <c r="BB24" s="8"/>
-      <c r="BC24" s="8"/>
-      <c r="BD24" s="8"/>
-      <c r="BE24" s="8"/>
-      <c r="BF24" s="8"/>
-      <c r="BG24" s="8"/>
-      <c r="BH24" s="8"/>
-    </row>
-    <row r="25" spans="1:60" s="28" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="21"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D25" s="14">
-        <f>AVERAGE(D19:D24)</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="F25" s="23">
-        <v>45923</v>
-      </c>
-      <c r="G25" s="23">
-        <v>45950</v>
-      </c>
-      <c r="H25" s="22">
-        <f>G25-F25</f>
-        <v>27</v>
-      </c>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="P25" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="8"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="8"/>
-      <c r="Y25" s="8"/>
-      <c r="Z25" s="8"/>
-      <c r="AA25" s="8"/>
-      <c r="AB25" s="8"/>
-      <c r="AC25" s="8"/>
-      <c r="AD25" s="8"/>
-      <c r="AE25" s="8"/>
-      <c r="AF25" s="8"/>
-      <c r="AG25" s="8"/>
-      <c r="AH25" s="8"/>
-      <c r="AI25" s="8"/>
-      <c r="AJ25" s="8"/>
-      <c r="AK25" s="8"/>
-      <c r="AL25" s="8"/>
-      <c r="AM25" s="8"/>
-      <c r="AN25" s="8"/>
-      <c r="AO25" s="8"/>
-      <c r="AP25" s="8"/>
-      <c r="AQ25" s="8"/>
-      <c r="AR25" s="8"/>
-      <c r="AS25" s="8"/>
-      <c r="AT25" s="8"/>
-      <c r="AU25" s="8"/>
-      <c r="AV25" s="8"/>
-      <c r="AW25" s="8"/>
-      <c r="AX25" s="8"/>
-      <c r="AY25" s="8"/>
-      <c r="AZ25" s="8"/>
-      <c r="BA25" s="8"/>
-      <c r="BB25" s="8"/>
-      <c r="BC25" s="8"/>
-      <c r="BD25" s="8"/>
-      <c r="BE25" s="8"/>
-      <c r="BF25" s="8"/>
-      <c r="BG25" s="8"/>
-      <c r="BH25" s="8"/>
-    </row>
-    <row r="26" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="8"/>
-      <c r="W26" s="8"/>
-      <c r="X26" s="8"/>
-      <c r="Y26" s="8"/>
-      <c r="Z26" s="8"/>
-      <c r="AA26" s="8"/>
-      <c r="AB26" s="8"/>
-      <c r="AC26" s="8"/>
-      <c r="AD26" s="8"/>
-      <c r="AE26" s="8"/>
-      <c r="AF26" s="8"/>
-      <c r="AG26" s="8"/>
-      <c r="AH26" s="8"/>
-      <c r="AI26" s="8"/>
-      <c r="AJ26" s="8"/>
-      <c r="AK26" s="8"/>
-      <c r="AL26" s="8"/>
-      <c r="AM26" s="8"/>
-      <c r="AN26" s="8"/>
-      <c r="AO26" s="8"/>
-      <c r="AP26" s="8"/>
-      <c r="AQ26" s="8"/>
-      <c r="AR26" s="8"/>
-      <c r="AS26" s="8"/>
-      <c r="AT26" s="8"/>
-      <c r="AU26" s="8"/>
-      <c r="AV26" s="8"/>
-      <c r="AW26" s="8"/>
-      <c r="AX26" s="8"/>
-      <c r="AY26" s="8"/>
-      <c r="AZ26" s="8"/>
-      <c r="BA26" s="8"/>
-      <c r="BB26" s="8"/>
-      <c r="BC26" s="8"/>
-      <c r="BD26" s="8"/>
-      <c r="BE26" s="8"/>
-      <c r="BF26" s="8"/>
-      <c r="BG26" s="8"/>
-      <c r="BH26" s="8"/>
-    </row>
-    <row r="27" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="13">
-        <v>14</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D27" s="14">
-        <v>0</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F27" s="10">
-        <v>45951</v>
-      </c>
-      <c r="G27" s="10">
-        <v>45955</v>
-      </c>
-      <c r="H27" s="13">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="I27" s="13">
-        <v>12</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="P27" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="8"/>
-      <c r="W27" s="8"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="8"/>
-      <c r="Z27" s="8"/>
-      <c r="AA27" s="8"/>
-      <c r="AB27" s="8"/>
-      <c r="AC27" s="8"/>
-      <c r="AD27" s="8"/>
-      <c r="AE27" s="8"/>
-      <c r="AF27" s="8"/>
-      <c r="AG27" s="8"/>
-      <c r="AH27" s="8"/>
-      <c r="AI27" s="8"/>
-      <c r="AJ27" s="8"/>
-      <c r="AK27" s="8"/>
-      <c r="AL27" s="8"/>
-      <c r="AM27" s="8"/>
-      <c r="AN27" s="8"/>
-      <c r="AO27" s="8"/>
-      <c r="AP27" s="8"/>
-      <c r="AQ27" s="8"/>
-      <c r="AR27" s="8"/>
-      <c r="AS27" s="8"/>
-      <c r="AT27" s="8"/>
-      <c r="AU27" s="8"/>
-      <c r="AV27" s="8"/>
-      <c r="AW27" s="8"/>
-      <c r="AX27" s="8"/>
-      <c r="AY27" s="8"/>
-      <c r="AZ27" s="8"/>
-      <c r="BA27" s="8"/>
-      <c r="BB27" s="8"/>
-      <c r="BC27" s="8"/>
-      <c r="BD27" s="8"/>
-      <c r="BE27" s="8"/>
-      <c r="BF27" s="8"/>
-      <c r="BG27" s="8"/>
-      <c r="BH27" s="8"/>
-    </row>
-    <row r="28" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="13">
-        <v>15</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="s">
-        <v>221</v>
-      </c>
-      <c r="D28" s="14">
-        <v>0</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="10">
-        <v>45956</v>
-      </c>
-      <c r="G28" s="10">
-        <v>45966</v>
-      </c>
-      <c r="H28" s="13">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="I28" s="13">
-        <v>30</v>
-      </c>
-      <c r="J28" t="s">
-        <v>203</v>
-      </c>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" t="s">
-        <v>187</v>
-      </c>
-      <c r="P28" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="8"/>
-      <c r="V28" s="8"/>
-      <c r="W28" s="8"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="8"/>
-      <c r="Z28" s="8"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="8"/>
-      <c r="AF28" s="8"/>
-      <c r="AG28" s="8"/>
-      <c r="AH28" s="8"/>
-      <c r="AI28" s="8"/>
-      <c r="AJ28" s="8"/>
-      <c r="AK28" s="8"/>
-      <c r="AL28" s="8"/>
-      <c r="AM28" s="8"/>
-      <c r="AN28" s="8"/>
-      <c r="AO28" s="8"/>
-      <c r="AP28" s="8"/>
-      <c r="AQ28" s="8"/>
-      <c r="AR28" s="8"/>
-      <c r="AS28" s="8"/>
-      <c r="AT28" s="8"/>
-      <c r="AU28" s="8"/>
-      <c r="AV28" s="8"/>
-      <c r="AW28" s="8"/>
-      <c r="AX28" s="8"/>
-      <c r="AY28" s="8"/>
-      <c r="AZ28" s="8"/>
-      <c r="BA28" s="8"/>
-      <c r="BB28" s="8"/>
-      <c r="BC28" s="8"/>
-      <c r="BD28" s="8"/>
-      <c r="BE28" s="8"/>
-      <c r="BF28" s="8"/>
-      <c r="BG28" s="8"/>
-      <c r="BH28" s="8"/>
-    </row>
-    <row r="29" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="13">
-        <v>16</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="D29" s="14">
-        <v>0</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="10">
-        <v>45967</v>
-      </c>
-      <c r="G29" s="10">
-        <v>45971</v>
-      </c>
-      <c r="H29" s="13">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="I29" s="13">
-        <v>16</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="P29" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="8"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="8"/>
-      <c r="V29" s="8"/>
-      <c r="W29" s="8"/>
-      <c r="X29" s="8"/>
-      <c r="Y29" s="8"/>
-      <c r="Z29" s="8"/>
-      <c r="AA29" s="8"/>
-      <c r="AB29" s="8"/>
-      <c r="AC29" s="8"/>
-      <c r="AD29" s="8"/>
-      <c r="AE29" s="8"/>
-      <c r="AF29" s="8"/>
-      <c r="AG29" s="8"/>
-      <c r="AH29" s="8"/>
-      <c r="AI29" s="8"/>
-      <c r="AJ29" s="8"/>
-      <c r="AK29" s="8"/>
-      <c r="AL29" s="8"/>
-      <c r="AM29" s="8"/>
-      <c r="AN29" s="8"/>
-      <c r="AO29" s="8"/>
-      <c r="AP29" s="8"/>
-      <c r="AQ29" s="8"/>
-      <c r="AR29" s="8"/>
-      <c r="AS29" s="8"/>
-      <c r="AT29" s="8"/>
-      <c r="AU29" s="8"/>
-      <c r="AV29" s="8"/>
-      <c r="AW29" s="8"/>
-      <c r="AX29" s="8"/>
-      <c r="AY29" s="8"/>
-      <c r="AZ29" s="8"/>
-      <c r="BA29" s="8"/>
-      <c r="BB29" s="8"/>
-      <c r="BC29" s="8"/>
-      <c r="BD29" s="8"/>
-      <c r="BE29" s="8"/>
-      <c r="BF29" s="8"/>
-      <c r="BG29" s="8"/>
-      <c r="BH29" s="8"/>
-    </row>
-    <row r="30" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="13">
-        <v>17</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" t="s">
-        <v>223</v>
-      </c>
-      <c r="D30" s="14">
-        <v>0</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="10">
-        <v>45956</v>
-      </c>
-      <c r="G30" s="10">
-        <v>45966</v>
-      </c>
-      <c r="H30" s="13">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="I30" s="13">
-        <v>24</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" t="s">
-        <v>189</v>
-      </c>
-      <c r="P30" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q30" s="8"/>
-      <c r="R30" s="8"/>
-      <c r="S30" s="8"/>
-      <c r="T30" s="8"/>
-      <c r="U30" s="8"/>
-      <c r="V30" s="8"/>
-      <c r="W30" s="8"/>
-      <c r="X30" s="8"/>
-      <c r="Y30" s="8"/>
-      <c r="Z30" s="8"/>
-      <c r="AA30" s="8"/>
-      <c r="AB30" s="8"/>
-      <c r="AC30" s="8"/>
-      <c r="AD30" s="8"/>
-      <c r="AE30" s="8"/>
-      <c r="AF30" s="8"/>
-      <c r="AG30" s="8"/>
-      <c r="AH30" s="8"/>
-      <c r="AI30" s="8"/>
-      <c r="AJ30" s="8"/>
-      <c r="AK30" s="8"/>
-      <c r="AL30" s="8"/>
-      <c r="AM30" s="8"/>
-      <c r="AN30" s="8"/>
-      <c r="AO30" s="8"/>
-      <c r="AP30" s="8"/>
-      <c r="AQ30" s="8"/>
-      <c r="AR30" s="8"/>
-      <c r="AS30" s="8"/>
-      <c r="AT30" s="8"/>
-      <c r="AU30" s="8"/>
-      <c r="AV30" s="8"/>
-      <c r="AW30" s="8"/>
-      <c r="AX30" s="8"/>
-      <c r="AY30" s="8"/>
-      <c r="AZ30" s="8"/>
-      <c r="BA30" s="8"/>
-      <c r="BB30" s="8"/>
-      <c r="BC30" s="8"/>
-      <c r="BD30" s="8"/>
-      <c r="BE30" s="8"/>
-      <c r="BF30" s="8"/>
-      <c r="BG30" s="8"/>
-      <c r="BH30" s="8"/>
-    </row>
-    <row r="31" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="13">
-        <v>18</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="D31" s="14">
-        <v>0</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F31" s="10">
-        <v>45972</v>
-      </c>
-      <c r="G31" s="10">
-        <v>45976</v>
-      </c>
-      <c r="H31" s="13">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="I31" s="13">
-        <v>20</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="P31" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="8"/>
-      <c r="S31" s="8"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="8"/>
-      <c r="V31" s="8"/>
-      <c r="W31" s="8"/>
-      <c r="X31" s="8"/>
-      <c r="Y31" s="8"/>
-      <c r="Z31" s="8"/>
-      <c r="AA31" s="8"/>
-      <c r="AB31" s="8"/>
-      <c r="AC31" s="8"/>
-      <c r="AD31" s="8"/>
-      <c r="AE31" s="8"/>
-      <c r="AF31" s="8"/>
-      <c r="AG31" s="8"/>
-      <c r="AH31" s="8"/>
-      <c r="AI31" s="8"/>
-      <c r="AJ31" s="8"/>
-      <c r="AK31" s="8"/>
-      <c r="AL31" s="8"/>
-      <c r="AM31" s="8"/>
-      <c r="AN31" s="8"/>
-      <c r="AO31" s="8"/>
-      <c r="AP31" s="8"/>
-      <c r="AQ31" s="8"/>
-      <c r="AR31" s="8"/>
-      <c r="AS31" s="8"/>
-      <c r="AT31" s="8"/>
-      <c r="AU31" s="8"/>
-      <c r="AV31" s="8"/>
-      <c r="AW31" s="8"/>
-      <c r="AX31" s="8"/>
-      <c r="AY31" s="8"/>
-      <c r="AZ31" s="8"/>
-      <c r="BA31" s="8"/>
-      <c r="BB31" s="8"/>
-      <c r="BC31" s="8"/>
-      <c r="BD31" s="8"/>
-      <c r="BE31" s="8"/>
-      <c r="BF31" s="8"/>
-      <c r="BG31" s="8"/>
-      <c r="BH31" s="8"/>
-    </row>
-    <row r="32" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="13">
-        <v>19</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C32" t="s">
-        <v>225</v>
-      </c>
-      <c r="D32" s="14">
-        <v>0</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F32" s="10">
-        <v>45977</v>
-      </c>
-      <c r="G32" s="10">
-        <v>45978</v>
-      </c>
-      <c r="H32" s="13">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="I32" s="13">
-        <v>10</v>
-      </c>
-      <c r="J32" t="s">
-        <v>206</v>
-      </c>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" t="s">
-        <v>191</v>
-      </c>
-      <c r="P32" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q32" s="8"/>
-      <c r="R32" s="8"/>
-      <c r="S32" s="8"/>
-      <c r="T32" s="8"/>
-      <c r="U32" s="8"/>
-      <c r="V32" s="8"/>
-      <c r="W32" s="8"/>
-      <c r="X32" s="8"/>
-      <c r="Y32" s="8"/>
-      <c r="Z32" s="8"/>
-      <c r="AA32" s="8"/>
-      <c r="AB32" s="8"/>
-      <c r="AC32" s="8"/>
-      <c r="AD32" s="8"/>
-      <c r="AE32" s="8"/>
-      <c r="AF32" s="8"/>
-      <c r="AG32" s="8"/>
-      <c r="AH32" s="8"/>
-      <c r="AI32" s="8"/>
-      <c r="AJ32" s="8"/>
-      <c r="AK32" s="8"/>
-      <c r="AL32" s="8"/>
-      <c r="AM32" s="8"/>
-      <c r="AN32" s="8"/>
-      <c r="AO32" s="8"/>
-      <c r="AP32" s="8"/>
-      <c r="AQ32" s="8"/>
-      <c r="AR32" s="8"/>
-      <c r="AS32" s="8"/>
-      <c r="AT32" s="8"/>
-      <c r="AU32" s="8"/>
-      <c r="AV32" s="8"/>
-      <c r="AW32" s="8"/>
-      <c r="AX32" s="8"/>
-      <c r="AY32" s="8"/>
-      <c r="AZ32" s="8"/>
-      <c r="BA32" s="8"/>
-      <c r="BB32" s="8"/>
-      <c r="BC32" s="8"/>
-      <c r="BD32" s="8"/>
-      <c r="BE32" s="8"/>
-      <c r="BF32" s="8"/>
-      <c r="BG32" s="8"/>
-      <c r="BH32" s="8"/>
-    </row>
-    <row r="33" spans="1:60" s="28" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="D33" s="14">
-        <f>AVERAGE(D27:D32)</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="F33" s="23">
-        <v>45951</v>
-      </c>
-      <c r="G33" s="23">
-        <v>45978</v>
-      </c>
-      <c r="H33" s="22">
-        <f t="shared" si="3"/>
-        <v>27</v>
-      </c>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21"/>
-      <c r="O33" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="P33" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q33" s="21"/>
-      <c r="R33" s="21"/>
-      <c r="S33" s="8"/>
-      <c r="T33" s="8"/>
-      <c r="U33" s="8"/>
-      <c r="V33" s="8"/>
-      <c r="W33" s="8"/>
-      <c r="X33" s="8"/>
-      <c r="Y33" s="8"/>
-      <c r="Z33" s="8"/>
-      <c r="AA33" s="8"/>
-      <c r="AB33" s="8"/>
-      <c r="AC33" s="8"/>
-      <c r="AD33" s="8"/>
-      <c r="AE33" s="8"/>
-      <c r="AF33" s="8"/>
-      <c r="AG33" s="8"/>
-      <c r="AH33" s="8"/>
-      <c r="AI33" s="8"/>
-      <c r="AJ33" s="8"/>
-      <c r="AK33" s="8"/>
-      <c r="AL33" s="8"/>
-      <c r="AM33" s="8"/>
-      <c r="AN33" s="8"/>
-      <c r="AO33" s="8"/>
-      <c r="AP33" s="8"/>
-      <c r="AQ33" s="8"/>
-      <c r="AR33" s="8"/>
-      <c r="AS33" s="8"/>
-      <c r="AT33" s="8"/>
-      <c r="AU33" s="8"/>
-      <c r="AV33" s="8"/>
-      <c r="AW33" s="8"/>
-      <c r="AX33" s="8"/>
-      <c r="AY33" s="8"/>
-      <c r="AZ33" s="8"/>
-      <c r="BA33" s="8"/>
-      <c r="BB33" s="8"/>
-      <c r="BC33" s="8"/>
-      <c r="BD33" s="8"/>
-      <c r="BE33" s="8"/>
-      <c r="BF33" s="8"/>
-      <c r="BG33" s="8"/>
-      <c r="BH33" s="8"/>
-    </row>
-    <row r="34" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A34" s="24"/>
-      <c r="B34" s="25"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="25"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25"/>
-      <c r="U34" s="25"/>
-      <c r="V34" s="25"/>
-      <c r="W34" s="25"/>
-    </row>
-    <row r="35" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="A34" s="21"/>
+      <c r="B34" s="22"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="22"/>
+      <c r="S34" s="22"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="22"/>
+      <c r="V34" s="22"/>
+      <c r="W34" s="22"/>
+    </row>
+    <row r="35" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="29"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="26"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="D36" s="29"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
+      <c r="D36" s="26"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
-    <row r="37" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="D37" s="29"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
+      <c r="D37" s="26"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="D38" s="29"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
+      <c r="D38" s="26"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="D39" s="29"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
+      <c r="D39" s="26"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
-    <row r="47" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:60" x14ac:dyDescent="0.25">
       <c r="AH47" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:60" x14ac:dyDescent="0.25">
       <c r="AH48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="34:34" x14ac:dyDescent="0.3">
+    <row r="49" spans="34:34" x14ac:dyDescent="0.25">
       <c r="AH49" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="AN6:AT6"/>
+    <mergeCell ref="AU6:BA6"/>
     <mergeCell ref="BB6:BH6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:E7"/>
@@ -9667,11 +6649,6 @@
     <mergeCell ref="S6:Y6"/>
     <mergeCell ref="Z6:AF6"/>
     <mergeCell ref="AG6:AM6"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="AN6:AT6"/>
-    <mergeCell ref="AU6:BA6"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="D9:D39">
@@ -9790,241 +6767,241 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4950CB7-2F94-4BB8-831A-222FD5C1C274}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:EG49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="31.88671875" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="1" customWidth="1"/>
-    <col min="6" max="7" width="10.77734375" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" customWidth="1"/>
-    <col min="10" max="10" width="14.77734375" customWidth="1"/>
-    <col min="11" max="14" width="10.33203125" customWidth="1"/>
-    <col min="15" max="16" width="20.77734375" customWidth="1"/>
-    <col min="17" max="18" width="11.77734375" customWidth="1"/>
-    <col min="19" max="137" width="3.77734375" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" customWidth="1"/>
+    <col min="4" max="5" width="10.7109375" style="1" customWidth="1"/>
+    <col min="6" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.28515625" customWidth="1"/>
+    <col min="15" max="16" width="20.7109375" customWidth="1"/>
+    <col min="17" max="18" width="11.7109375" customWidth="1"/>
+    <col min="19" max="137" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:137" s="15" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:137" s="15" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
-        <v>227</v>
-      </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-    </row>
-    <row r="3" spans="1:137" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-    </row>
-    <row r="4" spans="1:137" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="39" t="s">
-        <v>210</v>
-      </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-    </row>
-    <row r="6" spans="1:137" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:137" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:137" s="15" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+    </row>
+    <row r="3" spans="1:137" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+    </row>
+    <row r="4" spans="1:137" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+    </row>
+    <row r="6" spans="1:137" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6" s="3">
         <f>D7+B6</f>
-        <v>45899</v>
-      </c>
-      <c r="F6" s="36" t="s">
+        <v>46113</v>
+      </c>
+      <c r="F6" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="K6" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="K6" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="Q6" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="R6" s="36"/>
-      <c r="S6" s="33">
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="37"/>
+      <c r="Q6" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="R6" s="37"/>
+      <c r="S6" s="31">
         <f>S7</f>
-        <v>45899</v>
-      </c>
-      <c r="T6" s="33"/>
-      <c r="U6" s="33"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33">
+        <v>46113</v>
+      </c>
+      <c r="T6" s="31"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="31"/>
+      <c r="Y6" s="31"/>
+      <c r="Z6" s="31">
         <f>Z7</f>
-        <v>45906</v>
-      </c>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="33"/>
-      <c r="AE6" s="33"/>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="33">
+        <v>46120</v>
+      </c>
+      <c r="AA6" s="31"/>
+      <c r="AB6" s="31"/>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="31"/>
+      <c r="AE6" s="31"/>
+      <c r="AF6" s="31"/>
+      <c r="AG6" s="31">
         <f>AG7</f>
-        <v>45913</v>
-      </c>
-      <c r="AH6" s="33"/>
-      <c r="AI6" s="33"/>
-      <c r="AJ6" s="33"/>
-      <c r="AK6" s="33"/>
-      <c r="AL6" s="33"/>
-      <c r="AM6" s="33"/>
-      <c r="AN6" s="33">
+        <v>46127</v>
+      </c>
+      <c r="AH6" s="31"/>
+      <c r="AI6" s="31"/>
+      <c r="AJ6" s="31"/>
+      <c r="AK6" s="31"/>
+      <c r="AL6" s="31"/>
+      <c r="AM6" s="31"/>
+      <c r="AN6" s="31">
         <f>AN7</f>
-        <v>45920</v>
-      </c>
-      <c r="AO6" s="33"/>
-      <c r="AP6" s="33"/>
-      <c r="AQ6" s="33"/>
-      <c r="AR6" s="33"/>
-      <c r="AS6" s="33"/>
-      <c r="AT6" s="33"/>
-      <c r="AU6" s="33">
+        <v>46134</v>
+      </c>
+      <c r="AO6" s="31"/>
+      <c r="AP6" s="31"/>
+      <c r="AQ6" s="31"/>
+      <c r="AR6" s="31"/>
+      <c r="AS6" s="31"/>
+      <c r="AT6" s="31"/>
+      <c r="AU6" s="31">
         <f>AU7</f>
-        <v>45927</v>
-      </c>
-      <c r="AV6" s="33"/>
-      <c r="AW6" s="33"/>
-      <c r="AX6" s="33"/>
-      <c r="AY6" s="33"/>
-      <c r="AZ6" s="33"/>
-      <c r="BA6" s="33"/>
-      <c r="BB6" s="33">
+        <v>46141</v>
+      </c>
+      <c r="AV6" s="31"/>
+      <c r="AW6" s="31"/>
+      <c r="AX6" s="31"/>
+      <c r="AY6" s="31"/>
+      <c r="AZ6" s="31"/>
+      <c r="BA6" s="31"/>
+      <c r="BB6" s="31">
         <f>BB7</f>
-        <v>45934</v>
-      </c>
-      <c r="BC6" s="33"/>
-      <c r="BD6" s="33"/>
-      <c r="BE6" s="33"/>
-      <c r="BF6" s="33"/>
-      <c r="BG6" s="33"/>
-      <c r="BH6" s="33"/>
-      <c r="BI6" s="33">
+        <v>46148</v>
+      </c>
+      <c r="BC6" s="31"/>
+      <c r="BD6" s="31"/>
+      <c r="BE6" s="31"/>
+      <c r="BF6" s="31"/>
+      <c r="BG6" s="31"/>
+      <c r="BH6" s="31"/>
+      <c r="BI6" s="31">
         <f t="shared" ref="BI6" si="0">BI7</f>
-        <v>45941</v>
-      </c>
-      <c r="BJ6" s="33"/>
-      <c r="BK6" s="33"/>
-      <c r="BL6" s="33"/>
-      <c r="BM6" s="33"/>
-      <c r="BN6" s="33"/>
-      <c r="BO6" s="33"/>
-      <c r="BP6" s="33">
+        <v>46155</v>
+      </c>
+      <c r="BJ6" s="31"/>
+      <c r="BK6" s="31"/>
+      <c r="BL6" s="31"/>
+      <c r="BM6" s="31"/>
+      <c r="BN6" s="31"/>
+      <c r="BO6" s="31"/>
+      <c r="BP6" s="31">
         <f t="shared" ref="BP6" si="1">BP7</f>
-        <v>45948</v>
-      </c>
-      <c r="BQ6" s="33"/>
-      <c r="BR6" s="33"/>
-      <c r="BS6" s="33"/>
-      <c r="BT6" s="33"/>
-      <c r="BU6" s="33"/>
-      <c r="BV6" s="33"/>
-      <c r="BW6" s="33">
+        <v>46162</v>
+      </c>
+      <c r="BQ6" s="31"/>
+      <c r="BR6" s="31"/>
+      <c r="BS6" s="31"/>
+      <c r="BT6" s="31"/>
+      <c r="BU6" s="31"/>
+      <c r="BV6" s="31"/>
+      <c r="BW6" s="31">
         <f t="shared" ref="BW6" si="2">BW7</f>
-        <v>45955</v>
-      </c>
-      <c r="BX6" s="33"/>
-      <c r="BY6" s="33"/>
-      <c r="BZ6" s="33"/>
-      <c r="CA6" s="33"/>
-      <c r="CB6" s="33"/>
-      <c r="CC6" s="33"/>
-      <c r="CD6" s="33">
+        <v>46169</v>
+      </c>
+      <c r="BX6" s="31"/>
+      <c r="BY6" s="31"/>
+      <c r="BZ6" s="31"/>
+      <c r="CA6" s="31"/>
+      <c r="CB6" s="31"/>
+      <c r="CC6" s="31"/>
+      <c r="CD6" s="31">
         <f t="shared" ref="CD6" si="3">CD7</f>
-        <v>45962</v>
-      </c>
-      <c r="CE6" s="33"/>
-      <c r="CF6" s="33"/>
-      <c r="CG6" s="33"/>
-      <c r="CH6" s="33"/>
-      <c r="CI6" s="33"/>
-      <c r="CJ6" s="33"/>
-      <c r="CK6" s="33">
+        <v>46176</v>
+      </c>
+      <c r="CE6" s="31"/>
+      <c r="CF6" s="31"/>
+      <c r="CG6" s="31"/>
+      <c r="CH6" s="31"/>
+      <c r="CI6" s="31"/>
+      <c r="CJ6" s="31"/>
+      <c r="CK6" s="31">
         <f t="shared" ref="CK6" si="4">CK7</f>
-        <v>45969</v>
-      </c>
-      <c r="CL6" s="33"/>
-      <c r="CM6" s="33"/>
-      <c r="CN6" s="33"/>
-      <c r="CO6" s="33"/>
-      <c r="CP6" s="33"/>
-      <c r="CQ6" s="33"/>
-      <c r="CR6" s="33">
+        <v>46183</v>
+      </c>
+      <c r="CL6" s="31"/>
+      <c r="CM6" s="31"/>
+      <c r="CN6" s="31"/>
+      <c r="CO6" s="31"/>
+      <c r="CP6" s="31"/>
+      <c r="CQ6" s="31"/>
+      <c r="CR6" s="31">
         <f t="shared" ref="CR6" si="5">CR7</f>
-        <v>45976</v>
-      </c>
-      <c r="CS6" s="33"/>
-      <c r="CT6" s="33"/>
-      <c r="CU6" s="33"/>
-      <c r="CV6" s="33"/>
-      <c r="CW6" s="33"/>
-      <c r="CX6" s="33"/>
-      <c r="CY6" s="42"/>
-      <c r="CZ6" s="42"/>
-      <c r="DA6" s="42"/>
-      <c r="DB6" s="42"/>
-      <c r="DC6" s="42"/>
-      <c r="DD6" s="42"/>
-      <c r="DE6" s="42"/>
-      <c r="DF6" s="42"/>
-      <c r="DG6" s="42"/>
-      <c r="DH6" s="42"/>
-      <c r="DI6" s="42"/>
-      <c r="DJ6" s="42"/>
-      <c r="DK6" s="42"/>
-      <c r="DL6" s="42"/>
-      <c r="DM6" s="42"/>
-      <c r="DN6" s="42"/>
-      <c r="DO6" s="42"/>
-      <c r="DP6" s="42"/>
-      <c r="DQ6" s="42"/>
-      <c r="DR6" s="42"/>
-      <c r="DS6" s="42"/>
-      <c r="DT6" s="42"/>
-      <c r="DU6" s="42"/>
-      <c r="DV6" s="42"/>
-      <c r="DW6" s="42"/>
-      <c r="DX6" s="42"/>
-      <c r="DY6" s="42"/>
-      <c r="DZ6" s="42"/>
-      <c r="EA6" s="42"/>
-      <c r="EB6" s="42"/>
-      <c r="EC6" s="42"/>
-      <c r="ED6" s="42"/>
-      <c r="EE6" s="42"/>
-      <c r="EF6" s="42"/>
-      <c r="EG6" s="42"/>
-    </row>
-    <row r="7" spans="1:137" x14ac:dyDescent="0.3">
-      <c r="B7" s="37" t="s">
+        <v>46190</v>
+      </c>
+      <c r="CS6" s="31"/>
+      <c r="CT6" s="31"/>
+      <c r="CU6" s="31"/>
+      <c r="CV6" s="31"/>
+      <c r="CW6" s="31"/>
+      <c r="CX6" s="31"/>
+      <c r="CY6" s="30"/>
+      <c r="CZ6" s="30"/>
+      <c r="DA6" s="30"/>
+      <c r="DB6" s="30"/>
+      <c r="DC6" s="30"/>
+      <c r="DD6" s="30"/>
+      <c r="DE6" s="30"/>
+      <c r="DF6" s="30"/>
+      <c r="DG6" s="30"/>
+      <c r="DH6" s="30"/>
+      <c r="DI6" s="30"/>
+      <c r="DJ6" s="30"/>
+      <c r="DK6" s="30"/>
+      <c r="DL6" s="30"/>
+      <c r="DM6" s="30"/>
+      <c r="DN6" s="30"/>
+      <c r="DO6" s="30"/>
+      <c r="DP6" s="30"/>
+      <c r="DQ6" s="30"/>
+      <c r="DR6" s="30"/>
+      <c r="DS6" s="30"/>
+      <c r="DT6" s="30"/>
+      <c r="DU6" s="30"/>
+      <c r="DV6" s="30"/>
+      <c r="DW6" s="30"/>
+      <c r="DX6" s="30"/>
+      <c r="DY6" s="30"/>
+      <c r="DZ6" s="30"/>
+      <c r="EA6" s="30"/>
+      <c r="EB6" s="30"/>
+      <c r="EC6" s="30"/>
+      <c r="ED6" s="30"/>
+      <c r="EE6" s="30"/>
+      <c r="EF6" s="30"/>
+      <c r="EG6" s="30"/>
+    </row>
+    <row r="7" spans="1:137" x14ac:dyDescent="0.25">
+      <c r="B7" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="35">
-        <v>45899</v>
-      </c>
-      <c r="E7" s="35"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33">
+        <v>46113</v>
+      </c>
+      <c r="E7" s="33"/>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -10040,379 +7017,379 @@
       <c r="R7" s="17"/>
       <c r="S7" s="4">
         <f>C6</f>
-        <v>45899</v>
+        <v>46113</v>
       </c>
       <c r="T7" s="4">
         <f>S7+1</f>
-        <v>45900</v>
+        <v>46114</v>
       </c>
       <c r="U7" s="4">
         <f t="shared" ref="U7:AI7" si="6">T7+1</f>
-        <v>45901</v>
+        <v>46115</v>
       </c>
       <c r="V7" s="4">
         <f t="shared" si="6"/>
-        <v>45902</v>
+        <v>46116</v>
       </c>
       <c r="W7" s="4">
         <f t="shared" si="6"/>
-        <v>45903</v>
+        <v>46117</v>
       </c>
       <c r="X7" s="4">
         <f t="shared" si="6"/>
-        <v>45904</v>
+        <v>46118</v>
       </c>
       <c r="Y7" s="4">
         <f t="shared" si="6"/>
-        <v>45905</v>
+        <v>46119</v>
       </c>
       <c r="Z7" s="4">
         <f t="shared" si="6"/>
-        <v>45906</v>
+        <v>46120</v>
       </c>
       <c r="AA7" s="4">
         <f t="shared" si="6"/>
-        <v>45907</v>
+        <v>46121</v>
       </c>
       <c r="AB7" s="4">
         <f t="shared" si="6"/>
-        <v>45908</v>
+        <v>46122</v>
       </c>
       <c r="AC7" s="4">
         <f t="shared" si="6"/>
-        <v>45909</v>
+        <v>46123</v>
       </c>
       <c r="AD7" s="4">
         <f t="shared" si="6"/>
-        <v>45910</v>
+        <v>46124</v>
       </c>
       <c r="AE7" s="4">
         <f t="shared" si="6"/>
-        <v>45911</v>
+        <v>46125</v>
       </c>
       <c r="AF7" s="4">
         <f t="shared" si="6"/>
-        <v>45912</v>
+        <v>46126</v>
       </c>
       <c r="AG7" s="4">
         <f t="shared" si="6"/>
-        <v>45913</v>
+        <v>46127</v>
       </c>
       <c r="AH7" s="4">
         <f t="shared" si="6"/>
-        <v>45914</v>
+        <v>46128</v>
       </c>
       <c r="AI7" s="4">
         <f t="shared" si="6"/>
-        <v>45915</v>
+        <v>46129</v>
       </c>
       <c r="AJ7" s="4">
         <f>AI7+1</f>
-        <v>45916</v>
+        <v>46130</v>
       </c>
       <c r="AK7" s="4">
         <f t="shared" ref="AK7:BH7" si="7">AJ7+1</f>
-        <v>45917</v>
+        <v>46131</v>
       </c>
       <c r="AL7" s="4">
         <f t="shared" si="7"/>
-        <v>45918</v>
+        <v>46132</v>
       </c>
       <c r="AM7" s="4">
         <f t="shared" si="7"/>
-        <v>45919</v>
+        <v>46133</v>
       </c>
       <c r="AN7" s="4">
         <f t="shared" si="7"/>
-        <v>45920</v>
+        <v>46134</v>
       </c>
       <c r="AO7" s="4">
         <f t="shared" si="7"/>
-        <v>45921</v>
+        <v>46135</v>
       </c>
       <c r="AP7" s="4">
         <f t="shared" si="7"/>
-        <v>45922</v>
+        <v>46136</v>
       </c>
       <c r="AQ7" s="4">
         <f t="shared" si="7"/>
-        <v>45923</v>
+        <v>46137</v>
       </c>
       <c r="AR7" s="4">
         <f t="shared" si="7"/>
-        <v>45924</v>
+        <v>46138</v>
       </c>
       <c r="AS7" s="4">
         <f t="shared" si="7"/>
-        <v>45925</v>
+        <v>46139</v>
       </c>
       <c r="AT7" s="4">
         <f t="shared" si="7"/>
-        <v>45926</v>
+        <v>46140</v>
       </c>
       <c r="AU7" s="4">
         <f t="shared" si="7"/>
-        <v>45927</v>
+        <v>46141</v>
       </c>
       <c r="AV7" s="4">
         <f t="shared" si="7"/>
-        <v>45928</v>
+        <v>46142</v>
       </c>
       <c r="AW7" s="4">
         <f t="shared" si="7"/>
-        <v>45929</v>
+        <v>46143</v>
       </c>
       <c r="AX7" s="4">
         <f t="shared" si="7"/>
-        <v>45930</v>
+        <v>46144</v>
       </c>
       <c r="AY7" s="4">
         <f t="shared" si="7"/>
-        <v>45931</v>
+        <v>46145</v>
       </c>
       <c r="AZ7" s="4">
         <f t="shared" si="7"/>
-        <v>45932</v>
+        <v>46146</v>
       </c>
       <c r="BA7" s="4">
         <f t="shared" si="7"/>
-        <v>45933</v>
+        <v>46147</v>
       </c>
       <c r="BB7" s="4">
         <f t="shared" si="7"/>
-        <v>45934</v>
+        <v>46148</v>
       </c>
       <c r="BC7" s="4">
         <f t="shared" si="7"/>
-        <v>45935</v>
+        <v>46149</v>
       </c>
       <c r="BD7" s="4">
         <f t="shared" si="7"/>
-        <v>45936</v>
+        <v>46150</v>
       </c>
       <c r="BE7" s="4">
         <f t="shared" si="7"/>
-        <v>45937</v>
+        <v>46151</v>
       </c>
       <c r="BF7" s="4">
         <f t="shared" si="7"/>
-        <v>45938</v>
+        <v>46152</v>
       </c>
       <c r="BG7" s="4">
         <f t="shared" si="7"/>
-        <v>45939</v>
+        <v>46153</v>
       </c>
       <c r="BH7" s="4">
         <f t="shared" si="7"/>
-        <v>45940</v>
+        <v>46154</v>
       </c>
       <c r="BI7" s="4">
         <f t="shared" ref="BI7" si="8">BH7+1</f>
-        <v>45941</v>
+        <v>46155</v>
       </c>
       <c r="BJ7" s="4">
         <f t="shared" ref="BJ7" si="9">BI7+1</f>
-        <v>45942</v>
+        <v>46156</v>
       </c>
       <c r="BK7" s="4">
         <f t="shared" ref="BK7" si="10">BJ7+1</f>
-        <v>45943</v>
+        <v>46157</v>
       </c>
       <c r="BL7" s="4">
         <f t="shared" ref="BL7" si="11">BK7+1</f>
-        <v>45944</v>
+        <v>46158</v>
       </c>
       <c r="BM7" s="4">
         <f t="shared" ref="BM7" si="12">BL7+1</f>
-        <v>45945</v>
+        <v>46159</v>
       </c>
       <c r="BN7" s="4">
         <f t="shared" ref="BN7" si="13">BM7+1</f>
-        <v>45946</v>
+        <v>46160</v>
       </c>
       <c r="BO7" s="4">
         <f t="shared" ref="BO7" si="14">BN7+1</f>
-        <v>45947</v>
+        <v>46161</v>
       </c>
       <c r="BP7" s="4">
         <f t="shared" ref="BP7" si="15">BO7+1</f>
-        <v>45948</v>
+        <v>46162</v>
       </c>
       <c r="BQ7" s="4">
         <f t="shared" ref="BQ7" si="16">BP7+1</f>
-        <v>45949</v>
+        <v>46163</v>
       </c>
       <c r="BR7" s="4">
         <f t="shared" ref="BR7" si="17">BQ7+1</f>
-        <v>45950</v>
+        <v>46164</v>
       </c>
       <c r="BS7" s="4">
         <f t="shared" ref="BS7" si="18">BR7+1</f>
-        <v>45951</v>
+        <v>46165</v>
       </c>
       <c r="BT7" s="4">
         <f t="shared" ref="BT7" si="19">BS7+1</f>
-        <v>45952</v>
+        <v>46166</v>
       </c>
       <c r="BU7" s="4">
         <f t="shared" ref="BU7" si="20">BT7+1</f>
-        <v>45953</v>
+        <v>46167</v>
       </c>
       <c r="BV7" s="4">
         <f t="shared" ref="BV7" si="21">BU7+1</f>
-        <v>45954</v>
+        <v>46168</v>
       </c>
       <c r="BW7" s="4">
         <f t="shared" ref="BW7" si="22">BV7+1</f>
-        <v>45955</v>
+        <v>46169</v>
       </c>
       <c r="BX7" s="4">
         <f t="shared" ref="BX7" si="23">BW7+1</f>
-        <v>45956</v>
+        <v>46170</v>
       </c>
       <c r="BY7" s="4">
         <f t="shared" ref="BY7" si="24">BX7+1</f>
-        <v>45957</v>
+        <v>46171</v>
       </c>
       <c r="BZ7" s="4">
         <f t="shared" ref="BZ7" si="25">BY7+1</f>
-        <v>45958</v>
+        <v>46172</v>
       </c>
       <c r="CA7" s="4">
         <f t="shared" ref="CA7" si="26">BZ7+1</f>
-        <v>45959</v>
+        <v>46173</v>
       </c>
       <c r="CB7" s="4">
         <f t="shared" ref="CB7" si="27">CA7+1</f>
-        <v>45960</v>
+        <v>46174</v>
       </c>
       <c r="CC7" s="4">
         <f t="shared" ref="CC7" si="28">CB7+1</f>
-        <v>45961</v>
+        <v>46175</v>
       </c>
       <c r="CD7" s="4">
         <f t="shared" ref="CD7" si="29">CC7+1</f>
-        <v>45962</v>
+        <v>46176</v>
       </c>
       <c r="CE7" s="4">
         <f t="shared" ref="CE7" si="30">CD7+1</f>
-        <v>45963</v>
+        <v>46177</v>
       </c>
       <c r="CF7" s="4">
         <f t="shared" ref="CF7" si="31">CE7+1</f>
-        <v>45964</v>
+        <v>46178</v>
       </c>
       <c r="CG7" s="4">
         <f t="shared" ref="CG7" si="32">CF7+1</f>
-        <v>45965</v>
+        <v>46179</v>
       </c>
       <c r="CH7" s="4">
         <f t="shared" ref="CH7" si="33">CG7+1</f>
-        <v>45966</v>
+        <v>46180</v>
       </c>
       <c r="CI7" s="4">
         <f t="shared" ref="CI7" si="34">CH7+1</f>
-        <v>45967</v>
+        <v>46181</v>
       </c>
       <c r="CJ7" s="4">
         <f t="shared" ref="CJ7" si="35">CI7+1</f>
-        <v>45968</v>
+        <v>46182</v>
       </c>
       <c r="CK7" s="4">
         <f t="shared" ref="CK7" si="36">CJ7+1</f>
-        <v>45969</v>
+        <v>46183</v>
       </c>
       <c r="CL7" s="4">
         <f t="shared" ref="CL7" si="37">CK7+1</f>
-        <v>45970</v>
+        <v>46184</v>
       </c>
       <c r="CM7" s="4">
         <f t="shared" ref="CM7" si="38">CL7+1</f>
-        <v>45971</v>
+        <v>46185</v>
       </c>
       <c r="CN7" s="4">
         <f t="shared" ref="CN7" si="39">CM7+1</f>
-        <v>45972</v>
+        <v>46186</v>
       </c>
       <c r="CO7" s="4">
         <f t="shared" ref="CO7" si="40">CN7+1</f>
-        <v>45973</v>
+        <v>46187</v>
       </c>
       <c r="CP7" s="4">
         <f t="shared" ref="CP7" si="41">CO7+1</f>
-        <v>45974</v>
+        <v>46188</v>
       </c>
       <c r="CQ7" s="4">
         <f t="shared" ref="CQ7" si="42">CP7+1</f>
-        <v>45975</v>
+        <v>46189</v>
       </c>
       <c r="CR7" s="4">
         <f t="shared" ref="CR7" si="43">CQ7+1</f>
-        <v>45976</v>
+        <v>46190</v>
       </c>
       <c r="CS7" s="4">
         <f t="shared" ref="CS7" si="44">CR7+1</f>
-        <v>45977</v>
+        <v>46191</v>
       </c>
       <c r="CT7" s="4">
         <f t="shared" ref="CT7" si="45">CS7+1</f>
-        <v>45978</v>
+        <v>46192</v>
       </c>
       <c r="CU7" s="4">
         <f t="shared" ref="CU7" si="46">CT7+1</f>
-        <v>45979</v>
+        <v>46193</v>
       </c>
       <c r="CV7" s="4">
         <f t="shared" ref="CV7" si="47">CU7+1</f>
-        <v>45980</v>
+        <v>46194</v>
       </c>
       <c r="CW7" s="4">
         <f t="shared" ref="CW7" si="48">CV7+1</f>
-        <v>45981</v>
+        <v>46195</v>
       </c>
       <c r="CX7" s="4">
         <f t="shared" ref="CX7" si="49">CW7+1</f>
-        <v>45982</v>
-      </c>
-      <c r="CY7" s="32"/>
-      <c r="CZ7" s="32"/>
-      <c r="DA7" s="32"/>
-      <c r="DB7" s="32"/>
-      <c r="DC7" s="32"/>
-      <c r="DD7" s="32"/>
-      <c r="DE7" s="32"/>
-      <c r="DF7" s="32"/>
-      <c r="DG7" s="32"/>
-      <c r="DH7" s="32"/>
-      <c r="DI7" s="32"/>
-      <c r="DJ7" s="32"/>
-      <c r="DK7" s="32"/>
-      <c r="DL7" s="32"/>
-      <c r="DM7" s="32"/>
-      <c r="DN7" s="32"/>
-      <c r="DO7" s="32"/>
-      <c r="DP7" s="32"/>
-      <c r="DQ7" s="32"/>
-      <c r="DR7" s="32"/>
-      <c r="DS7" s="32"/>
-      <c r="DT7" s="32"/>
-      <c r="DU7" s="32"/>
-      <c r="DV7" s="32"/>
-      <c r="DW7" s="32"/>
-      <c r="DX7" s="32"/>
-      <c r="DY7" s="32"/>
-      <c r="DZ7" s="32"/>
-      <c r="EA7" s="32"/>
-      <c r="EB7" s="32"/>
-      <c r="EC7" s="32"/>
-      <c r="ED7" s="32"/>
-      <c r="EE7" s="32"/>
-      <c r="EF7" s="32"/>
-      <c r="EG7" s="32"/>
-    </row>
-    <row r="8" spans="1:137" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>46196</v>
+      </c>
+      <c r="CY7" s="29"/>
+      <c r="CZ7" s="29"/>
+      <c r="DA7" s="29"/>
+      <c r="DB7" s="29"/>
+      <c r="DC7" s="29"/>
+      <c r="DD7" s="29"/>
+      <c r="DE7" s="29"/>
+      <c r="DF7" s="29"/>
+      <c r="DG7" s="29"/>
+      <c r="DH7" s="29"/>
+      <c r="DI7" s="29"/>
+      <c r="DJ7" s="29"/>
+      <c r="DK7" s="29"/>
+      <c r="DL7" s="29"/>
+      <c r="DM7" s="29"/>
+      <c r="DN7" s="29"/>
+      <c r="DO7" s="29"/>
+      <c r="DP7" s="29"/>
+      <c r="DQ7" s="29"/>
+      <c r="DR7" s="29"/>
+      <c r="DS7" s="29"/>
+      <c r="DT7" s="29"/>
+      <c r="DU7" s="29"/>
+      <c r="DV7" s="29"/>
+      <c r="DW7" s="29"/>
+      <c r="DX7" s="29"/>
+      <c r="DY7" s="29"/>
+      <c r="DZ7" s="29"/>
+      <c r="EA7" s="29"/>
+      <c r="EB7" s="29"/>
+      <c r="EC7" s="29"/>
+      <c r="ED7" s="29"/>
+      <c r="EE7" s="29"/>
+      <c r="EF7" s="29"/>
+      <c r="EG7" s="29"/>
+    </row>
+    <row r="8" spans="1:137" s="15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>26</v>
@@ -10424,7 +7401,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>3</v>
@@ -10433,13 +7410,13 @@
         <v>4</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>3</v>
@@ -10448,365 +7425,365 @@
         <v>4</v>
       </c>
       <c r="M8" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="O8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="Q8" s="2" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="S8" s="2" t="str">
         <f>UPPER(LEFT(TEXT(S7,"ddd"),1))</f>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="T8" s="2" t="str">
         <f t="shared" ref="T8:BH8" si="50">UPPER(LEFT(TEXT(T7,"ddd"),1))</f>
-        <v>D</v>
+        <v>J</v>
       </c>
       <c r="U8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>L</v>
+        <v>V</v>
       </c>
       <c r="V8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="W8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="X8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>J</v>
+        <v>L</v>
       </c>
       <c r="Y8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>V</v>
+        <v>M</v>
       </c>
       <c r="Z8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AA8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>D</v>
+        <v>J</v>
       </c>
       <c r="AB8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>L</v>
+        <v>V</v>
       </c>
       <c r="AC8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="AD8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="AE8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>J</v>
+        <v>L</v>
       </c>
       <c r="AF8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>V</v>
+        <v>M</v>
       </c>
       <c r="AG8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AH8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>D</v>
+        <v>J</v>
       </c>
       <c r="AI8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>L</v>
+        <v>V</v>
       </c>
       <c r="AJ8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="AK8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="AL8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>J</v>
+        <v>L</v>
       </c>
       <c r="AM8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>V</v>
+        <v>M</v>
       </c>
       <c r="AN8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AO8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>D</v>
+        <v>J</v>
       </c>
       <c r="AP8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>L</v>
+        <v>V</v>
       </c>
       <c r="AQ8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="AR8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="AS8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>J</v>
+        <v>L</v>
       </c>
       <c r="AT8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>V</v>
+        <v>M</v>
       </c>
       <c r="AU8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AV8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>D</v>
+        <v>J</v>
       </c>
       <c r="AW8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>L</v>
+        <v>V</v>
       </c>
       <c r="AX8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="AY8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="AZ8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>J</v>
+        <v>L</v>
       </c>
       <c r="BA8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>V</v>
+        <v>M</v>
       </c>
       <c r="BB8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BC8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>D</v>
+        <v>J</v>
       </c>
       <c r="BD8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>L</v>
+        <v>V</v>
       </c>
       <c r="BE8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="BF8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="BG8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>J</v>
+        <v>L</v>
       </c>
       <c r="BH8" s="2" t="str">
         <f t="shared" si="50"/>
-        <v>V</v>
+        <v>M</v>
       </c>
       <c r="BI8" s="2" t="str">
         <f t="shared" ref="BI8:CC8" si="51">UPPER(LEFT(TEXT(BI7,"ddd"),1))</f>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BJ8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>D</v>
+        <v>J</v>
       </c>
       <c r="BK8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>L</v>
+        <v>V</v>
       </c>
       <c r="BL8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="BM8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="BN8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>J</v>
+        <v>L</v>
       </c>
       <c r="BO8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>V</v>
+        <v>M</v>
       </c>
       <c r="BP8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BQ8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>D</v>
+        <v>J</v>
       </c>
       <c r="BR8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>L</v>
+        <v>V</v>
       </c>
       <c r="BS8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="BT8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="BU8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>J</v>
+        <v>L</v>
       </c>
       <c r="BV8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>V</v>
+        <v>M</v>
       </c>
       <c r="BW8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BX8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>D</v>
+        <v>J</v>
       </c>
       <c r="BY8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>L</v>
+        <v>V</v>
       </c>
       <c r="BZ8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="CA8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="CB8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>J</v>
+        <v>L</v>
       </c>
       <c r="CC8" s="2" t="str">
         <f t="shared" si="51"/>
-        <v>V</v>
+        <v>M</v>
       </c>
       <c r="CD8" s="2" t="str">
         <f t="shared" ref="CD8:CX8" si="52">UPPER(LEFT(TEXT(CD7,"ddd"),1))</f>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="CE8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>D</v>
+        <v>J</v>
       </c>
       <c r="CF8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>L</v>
+        <v>V</v>
       </c>
       <c r="CG8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="CH8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="CI8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>J</v>
+        <v>L</v>
       </c>
       <c r="CJ8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>V</v>
+        <v>M</v>
       </c>
       <c r="CK8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="CL8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>D</v>
+        <v>J</v>
       </c>
       <c r="CM8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>L</v>
+        <v>V</v>
       </c>
       <c r="CN8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="CO8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="CP8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>J</v>
+        <v>L</v>
       </c>
       <c r="CQ8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>V</v>
+        <v>M</v>
       </c>
       <c r="CR8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="CS8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>D</v>
+        <v>J</v>
       </c>
       <c r="CT8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>L</v>
+        <v>V</v>
       </c>
       <c r="CU8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="CV8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="CW8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>J</v>
+        <v>L</v>
       </c>
       <c r="CX8" s="2" t="str">
         <f t="shared" si="52"/>
-        <v>V</v>
-      </c>
-    </row>
-    <row r="9" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="9" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="7" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="13"/>
@@ -10821,7 +7798,7 @@
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
@@ -10910,7 +7887,7 @@
       <c r="CW9" s="8"/>
       <c r="CX9" s="8"/>
     </row>
-    <row r="10" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>1</v>
       </c>
@@ -10918,7 +7895,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D10" s="14">
         <v>0</v>
@@ -10927,30 +7904,30 @@
         <v>9</v>
       </c>
       <c r="F10" s="10">
-        <v>45901</v>
+        <v>46113</v>
       </c>
       <c r="G10" s="10">
-        <v>45918</v>
+        <v>46116</v>
       </c>
       <c r="H10" s="13">
         <f>G10-F10+1</f>
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I10" s="13">
         <v>8</v>
       </c>
       <c r="J10" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>228</v>
+        <v>151</v>
       </c>
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
@@ -11039,7 +8016,7 @@
       <c r="CW10" s="8"/>
       <c r="CX10" s="8"/>
     </row>
-    <row r="11" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>2</v>
       </c>
@@ -11047,7 +8024,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D11" s="14">
         <v>0</v>
@@ -11056,10 +8033,10 @@
         <v>9</v>
       </c>
       <c r="F11" s="10">
-        <v>45905</v>
+        <v>46117</v>
       </c>
       <c r="G11" s="10">
-        <v>45915</v>
+        <v>46127</v>
       </c>
       <c r="H11" s="13">
         <f t="shared" ref="H11:H17" si="53">G11-F11+1</f>
@@ -11069,17 +8046,17 @@
         <v>12</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
       <c r="O11" s="8" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
@@ -11168,7 +8145,7 @@
       <c r="CW11" s="8"/>
       <c r="CX11" s="8"/>
     </row>
-    <row r="12" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>3</v>
       </c>
@@ -11176,7 +8153,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="D12" s="14">
         <v>0</v>
@@ -11185,10 +8162,10 @@
         <v>10</v>
       </c>
       <c r="F12" s="10">
-        <v>45901</v>
+        <v>46113</v>
       </c>
       <c r="G12" s="10">
-        <v>45904</v>
+        <v>46116</v>
       </c>
       <c r="H12" s="13">
         <f t="shared" si="53"/>
@@ -11198,14 +8175,14 @@
         <v>6</v>
       </c>
       <c r="J12" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
       <c r="P12" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
@@ -11294,7 +8271,7 @@
       <c r="CW12" s="8"/>
       <c r="CX12" s="8"/>
     </row>
-    <row r="13" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>4</v>
       </c>
@@ -11302,7 +8279,7 @@
         <v>8</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="D13" s="14">
         <v>0</v>
@@ -11311,30 +8288,30 @@
         <v>9</v>
       </c>
       <c r="F13" s="10">
-        <v>45905</v>
+        <v>46117</v>
       </c>
       <c r="G13" s="10">
-        <v>45921</v>
+        <v>46127</v>
       </c>
       <c r="H13" s="13">
         <f t="shared" si="53"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I13" s="13">
         <v>10</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
       <c r="O13" s="8" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
@@ -11423,15 +8400,15 @@
       <c r="CW13" s="8"/>
       <c r="CX13" s="8"/>
     </row>
-    <row r="14" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>5</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D14" s="14">
         <v>0</v>
@@ -11440,30 +8417,30 @@
         <v>10</v>
       </c>
       <c r="F14" s="10">
-        <v>45917</v>
+        <v>46122</v>
       </c>
       <c r="G14" s="10">
-        <v>45918</v>
+        <v>46125</v>
       </c>
       <c r="H14" s="13">
         <f t="shared" si="53"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I14" s="13">
         <v>12</v>
       </c>
       <c r="J14" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
       <c r="O14" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
@@ -11552,15 +8529,15 @@
       <c r="CW14" s="8"/>
       <c r="CX14" s="8"/>
     </row>
-    <row r="15" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <v>6</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D15" s="14">
         <v>0</v>
@@ -11569,30 +8546,30 @@
         <v>10</v>
       </c>
       <c r="F15" s="10">
-        <v>45919</v>
+        <v>46122</v>
       </c>
       <c r="G15" s="10">
-        <v>45920</v>
+        <v>46127</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="53"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I15" s="13">
         <v>14</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
       <c r="O15" s="8" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>229</v>
+        <v>151</v>
       </c>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
@@ -11681,15 +8658,15 @@
       <c r="CW15" s="8"/>
       <c r="CX15" s="8"/>
     </row>
-    <row r="16" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <v>7</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C16" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D16" s="14">
         <v>0</v>
@@ -11698,30 +8675,30 @@
         <v>57</v>
       </c>
       <c r="F16" s="10">
-        <v>45921</v>
+        <v>46128</v>
       </c>
       <c r="G16" s="10">
-        <v>45922</v>
+        <v>46139</v>
       </c>
       <c r="H16" s="13">
         <f t="shared" si="53"/>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I16" s="13">
         <v>16</v>
       </c>
       <c r="J16" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
       <c r="O16" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
@@ -11810,46 +8787,46 @@
       <c r="CW16" s="8"/>
       <c r="CX16" s="8"/>
     </row>
-    <row r="17" spans="1:137" s="28" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21" t="s">
-        <v>178</v>
+    <row r="17" spans="1:137" s="25" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18" t="s">
+        <v>164</v>
       </c>
       <c r="D17" s="14">
         <f>AVERAGE(D10:D16)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="23">
-        <v>45901</v>
-      </c>
-      <c r="G17" s="23">
-        <v>45922</v>
-      </c>
-      <c r="H17" s="22">
+      <c r="F17" s="20">
+        <v>46113</v>
+      </c>
+      <c r="G17" s="20">
+        <v>46139</v>
+      </c>
+      <c r="H17" s="19">
         <f t="shared" si="53"/>
-        <v>22</v>
-      </c>
-      <c r="I17" s="22">
+        <v>27</v>
+      </c>
+      <c r="I17" s="19">
         <f>SUM(I10:I16)</f>
         <v>78</v>
       </c>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21" t="s">
-        <v>179</v>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18" t="s">
+        <v>165</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
+        <v>151</v>
+      </c>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18"/>
       <c r="S17" s="8"/>
       <c r="T17" s="8"/>
       <c r="U17" s="8"/>
@@ -11970,11 +8947,11 @@
       <c r="EF17"/>
       <c r="EG17"/>
     </row>
-    <row r="18" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="7" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="13"/>
@@ -11989,7 +8966,7 @@
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
@@ -12078,7 +9055,7 @@
       <c r="CW18" s="8"/>
       <c r="CX18" s="8"/>
     </row>
-    <row r="19" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>8</v>
       </c>
@@ -12086,7 +9063,7 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="D19" s="14">
         <v>0</v>
@@ -12095,10 +9072,10 @@
         <v>57</v>
       </c>
       <c r="F19" s="10">
-        <v>45921</v>
+        <v>46142</v>
       </c>
       <c r="G19" s="10">
-        <v>45925</v>
+        <v>46146</v>
       </c>
       <c r="H19" s="13">
         <f>G19-F19+1</f>
@@ -12108,14 +9085,14 @@
         <v>14</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
       <c r="P19" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
@@ -12204,7 +9181,7 @@
       <c r="CW19" s="8"/>
       <c r="CX19" s="8"/>
     </row>
-    <row r="20" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
         <v>9</v>
       </c>
@@ -12212,7 +9189,7 @@
         <v>12</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="D20" s="14">
         <v>0</v>
@@ -12221,10 +9198,10 @@
         <v>57</v>
       </c>
       <c r="F20" s="10">
-        <v>45926</v>
+        <v>46121</v>
       </c>
       <c r="G20" s="10">
-        <v>45930</v>
+        <v>46125</v>
       </c>
       <c r="H20" s="13">
         <f t="shared" ref="H20:H25" si="54">G20-F20+1</f>
@@ -12234,17 +9211,17 @@
         <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
       <c r="O20" s="8" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
@@ -12333,7 +9310,7 @@
       <c r="CW20" s="8"/>
       <c r="CX20" s="8"/>
     </row>
-    <row r="21" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
         <v>10</v>
       </c>
@@ -12341,7 +9318,7 @@
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="D21" s="14">
         <v>0</v>
@@ -12350,10 +9327,10 @@
         <v>10</v>
       </c>
       <c r="F21" s="10">
-        <v>45931</v>
+        <v>46148</v>
       </c>
       <c r="G21" s="10">
-        <v>45936</v>
+        <v>46153</v>
       </c>
       <c r="H21" s="13">
         <f t="shared" si="54"/>
@@ -12363,14 +9340,14 @@
         <v>20</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
       <c r="P21" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
@@ -12459,15 +9436,15 @@
       <c r="CW21" s="8"/>
       <c r="CX21" s="8"/>
     </row>
-    <row r="22" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
         <v>11</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D22" s="14">
         <v>0</v>
@@ -12476,10 +9453,10 @@
         <v>9</v>
       </c>
       <c r="F22" s="10">
-        <v>45931</v>
+        <v>46148</v>
       </c>
       <c r="G22" s="10">
-        <v>45938</v>
+        <v>46155</v>
       </c>
       <c r="H22" s="13">
         <f t="shared" si="54"/>
@@ -12489,17 +9466,17 @@
         <v>22</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
       <c r="O22" s="8" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
@@ -12588,15 +9565,15 @@
       <c r="CW22" s="8"/>
       <c r="CX22" s="8"/>
     </row>
-    <row r="23" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
         <v>12</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="D23" s="14">
         <v>0</v>
@@ -12605,10 +9582,10 @@
         <v>9</v>
       </c>
       <c r="F23" s="10">
-        <v>45939</v>
+        <v>46156</v>
       </c>
       <c r="G23" s="10">
-        <v>45942</v>
+        <v>46159</v>
       </c>
       <c r="H23" s="13">
         <f t="shared" si="54"/>
@@ -12618,17 +9595,17 @@
         <v>10</v>
       </c>
       <c r="J23" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
       <c r="O23" s="8" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="P23" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
@@ -12717,15 +9694,15 @@
       <c r="CW23" s="8"/>
       <c r="CX23" s="8"/>
     </row>
-    <row r="24" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
         <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C24" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="D24" s="14">
         <v>0</v>
@@ -12734,30 +9711,30 @@
         <v>57</v>
       </c>
       <c r="F24" s="10">
-        <v>45943</v>
+        <v>46160</v>
       </c>
       <c r="G24" s="10">
-        <v>45948</v>
+        <v>46167</v>
       </c>
       <c r="H24" s="13">
         <f t="shared" si="54"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I24" s="13">
         <v>20</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="P24" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
@@ -12846,46 +9823,46 @@
       <c r="CW24" s="8"/>
       <c r="CX24" s="8"/>
     </row>
-    <row r="25" spans="1:137" s="28" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="21"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21" t="s">
-        <v>185</v>
+    <row r="25" spans="1:137" s="25" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18" t="s">
+        <v>171</v>
       </c>
       <c r="D25" s="14">
         <f>AVERAGE(D19:D24)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="E25" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="23">
-        <v>45923</v>
-      </c>
-      <c r="G25" s="23">
-        <v>45950</v>
-      </c>
-      <c r="H25" s="22">
+      <c r="F25" s="20">
+        <v>46139</v>
+      </c>
+      <c r="G25" s="20">
+        <v>46174</v>
+      </c>
+      <c r="H25" s="19">
         <f t="shared" si="54"/>
-        <v>28</v>
-      </c>
-      <c r="I25" s="22">
+        <v>36</v>
+      </c>
+      <c r="I25" s="19">
         <f>SUM(I19:I24)</f>
         <v>104</v>
       </c>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21" t="s">
-        <v>194</v>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18" t="s">
+        <v>180</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
+        <v>151</v>
+      </c>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="18"/>
       <c r="S25" s="8"/>
       <c r="T25" s="8"/>
       <c r="U25" s="8"/>
@@ -13006,11 +9983,11 @@
       <c r="EF25"/>
       <c r="EG25"/>
     </row>
-    <row r="26" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="7" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="13"/>
@@ -13025,7 +10002,7 @@
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
       <c r="P26" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q26" s="8"/>
       <c r="R26" s="8"/>
@@ -13114,7 +10091,7 @@
       <c r="CW26" s="8"/>
       <c r="CX26" s="8"/>
     </row>
-    <row r="27" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
         <v>14</v>
       </c>
@@ -13122,7 +10099,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D27" s="14">
         <v>0</v>
@@ -13131,30 +10108,30 @@
         <v>57</v>
       </c>
       <c r="F27" s="10">
-        <v>45951</v>
+        <v>46175</v>
       </c>
       <c r="G27" s="10">
-        <v>45955</v>
+        <v>46180</v>
       </c>
       <c r="H27" s="13">
         <f>G27-F27+1</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I27" s="13">
         <v>12</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
       <c r="O27" s="8" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
@@ -13243,7 +10220,7 @@
       <c r="CW27" s="8"/>
       <c r="CX27" s="8"/>
     </row>
-    <row r="28" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
         <v>15</v>
       </c>
@@ -13251,7 +10228,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="D28" s="14">
         <v>0</v>
@@ -13260,30 +10237,30 @@
         <v>9</v>
       </c>
       <c r="F28" s="10">
-        <v>45956</v>
+        <v>46179</v>
       </c>
       <c r="G28" s="10">
-        <v>45966</v>
+        <v>46188</v>
       </c>
       <c r="H28" s="13">
         <f t="shared" ref="H28:H32" si="55">G28-F28+1</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I28" s="13">
         <v>30</v>
       </c>
       <c r="J28" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
       <c r="M28" s="8"/>
       <c r="N28" s="8"/>
       <c r="O28" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
@@ -13372,7 +10349,7 @@
       <c r="CW28" s="8"/>
       <c r="CX28" s="8"/>
     </row>
-    <row r="29" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
         <v>16</v>
       </c>
@@ -13380,7 +10357,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D29" s="14">
         <v>0</v>
@@ -13389,10 +10366,10 @@
         <v>9</v>
       </c>
       <c r="F29" s="10">
-        <v>45967</v>
+        <v>46189</v>
       </c>
       <c r="G29" s="10">
-        <v>45971</v>
+        <v>46193</v>
       </c>
       <c r="H29" s="13">
         <f t="shared" si="55"/>
@@ -13402,17 +10379,17 @@
         <v>16</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
       <c r="N29" s="8"/>
       <c r="O29" s="8" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q29" s="8"/>
       <c r="R29" s="8"/>
@@ -13501,7 +10478,7 @@
       <c r="CW29" s="8"/>
       <c r="CX29" s="8"/>
     </row>
-    <row r="30" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
         <v>17</v>
       </c>
@@ -13509,7 +10486,7 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D30" s="14">
         <v>0</v>
@@ -13518,30 +10495,30 @@
         <v>10</v>
       </c>
       <c r="F30" s="10">
-        <v>45956</v>
+        <v>46179</v>
       </c>
       <c r="G30" s="10">
-        <v>45966</v>
+        <v>46188</v>
       </c>
       <c r="H30" s="13">
         <f t="shared" si="55"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I30" s="13">
         <v>24</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
       <c r="O30" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="P30" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
@@ -13630,7 +10607,7 @@
       <c r="CW30" s="8"/>
       <c r="CX30" s="8"/>
     </row>
-    <row r="31" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="13">
         <v>18</v>
       </c>
@@ -13638,7 +10615,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D31" s="14">
         <v>0</v>
@@ -13647,30 +10624,30 @@
         <v>57</v>
       </c>
       <c r="F31" s="10">
-        <v>45972</v>
+        <v>46185</v>
       </c>
       <c r="G31" s="10">
-        <v>45976</v>
+        <v>46198</v>
       </c>
       <c r="H31" s="13">
         <f t="shared" si="55"/>
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I31" s="13">
         <v>20</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
       <c r="O31" s="8" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="P31" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q31" s="8"/>
       <c r="R31" s="8"/>
@@ -13759,15 +10736,15 @@
       <c r="CW31" s="8"/>
       <c r="CX31" s="8"/>
     </row>
-    <row r="32" spans="1:137" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:137" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13">
         <v>19</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C32" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="D32" s="14">
         <v>0</v>
@@ -13776,30 +10753,30 @@
         <v>57</v>
       </c>
       <c r="F32" s="10">
-        <v>45977</v>
+        <v>46189</v>
       </c>
       <c r="G32" s="10">
-        <v>45978</v>
+        <v>46202</v>
       </c>
       <c r="H32" s="13">
         <f t="shared" si="55"/>
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I32" s="13">
         <v>10</v>
       </c>
       <c r="J32" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
       <c r="M32" s="8"/>
       <c r="N32" s="8"/>
       <c r="O32" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
@@ -13888,46 +10865,46 @@
       <c r="CW32" s="8"/>
       <c r="CX32" s="8"/>
     </row>
-    <row r="33" spans="1:137" s="28" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21" t="s">
-        <v>192</v>
+    <row r="33" spans="1:137" s="25" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18" t="s">
+        <v>178</v>
       </c>
       <c r="D33" s="14">
         <f>AVERAGE(D27:D32)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F33" s="23">
-        <v>45951</v>
-      </c>
-      <c r="G33" s="23">
-        <v>45978</v>
-      </c>
-      <c r="H33" s="22">
+      <c r="F33" s="20">
+        <v>46175</v>
+      </c>
+      <c r="G33" s="20">
+        <v>46202</v>
+      </c>
+      <c r="H33" s="19">
         <f>G33-F33+1</f>
         <v>28</v>
       </c>
-      <c r="I33" s="22">
+      <c r="I33" s="19">
         <f>SUM(I27:I32)</f>
         <v>112</v>
       </c>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21"/>
-      <c r="O33" s="21" t="s">
-        <v>193</v>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18" t="s">
+        <v>179</v>
       </c>
       <c r="P33" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q33" s="21"/>
-      <c r="R33" s="21"/>
+        <v>151</v>
+      </c>
+      <c r="Q33" s="18"/>
+      <c r="R33" s="18"/>
       <c r="S33" s="8"/>
       <c r="T33" s="8"/>
       <c r="U33" s="8"/>
@@ -14048,89 +11025,107 @@
       <c r="EF33"/>
       <c r="EG33"/>
     </row>
-    <row r="34" spans="1:137" x14ac:dyDescent="0.3">
-      <c r="A34" s="24"/>
-      <c r="B34" s="25"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="25"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25"/>
-      <c r="U34" s="25"/>
-      <c r="V34" s="25"/>
-      <c r="W34" s="25"/>
-    </row>
-    <row r="35" spans="1:137" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:137" x14ac:dyDescent="0.25">
+      <c r="A34" s="21"/>
+      <c r="B34" s="22"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="22"/>
+      <c r="S34" s="22"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="22"/>
+      <c r="V34" s="22"/>
+      <c r="W34" s="22"/>
+    </row>
+    <row r="35" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="29"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="26"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" spans="1:137" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="D36" s="29"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
+      <c r="D36" s="26"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
-    <row r="37" spans="1:137" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="D37" s="29"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
+      <c r="D37" s="26"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" spans="1:137" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="D38" s="29"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
+      <c r="D38" s="26"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" spans="1:137" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="D39" s="29"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
+      <c r="D39" s="26"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
-    <row r="47" spans="1:137" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:137" x14ac:dyDescent="0.25">
       <c r="AH47" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:137" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:137" x14ac:dyDescent="0.25">
       <c r="AH48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="34:34" x14ac:dyDescent="0.3">
+    <row r="49" spans="34:34" x14ac:dyDescent="0.25">
       <c r="AH49" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="CD6:CJ6"/>
+    <mergeCell ref="S6:Y6"/>
+    <mergeCell ref="Z6:AF6"/>
+    <mergeCell ref="AG6:AM6"/>
+    <mergeCell ref="AN6:AT6"/>
+    <mergeCell ref="AU6:BA6"/>
+    <mergeCell ref="BB6:BH6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="BI6:BO6"/>
+    <mergeCell ref="BP6:BV6"/>
+    <mergeCell ref="BW6:CC6"/>
+    <mergeCell ref="Q6:R6"/>
     <mergeCell ref="EA6:EG6"/>
     <mergeCell ref="CK6:CQ6"/>
     <mergeCell ref="CR6:CX6"/>
@@ -14138,24 +11133,6 @@
     <mergeCell ref="DF6:DL6"/>
     <mergeCell ref="DM6:DS6"/>
     <mergeCell ref="DT6:DZ6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="BI6:BO6"/>
-    <mergeCell ref="BP6:BV6"/>
-    <mergeCell ref="BW6:CC6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="CD6:CJ6"/>
-    <mergeCell ref="S6:Y6"/>
-    <mergeCell ref="Z6:AF6"/>
-    <mergeCell ref="AG6:AM6"/>
-    <mergeCell ref="AN6:AT6"/>
-    <mergeCell ref="AU6:BA6"/>
-    <mergeCell ref="BB6:BH6"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="K6:N6"/>
   </mergeCells>
   <conditionalFormatting sqref="D9:D39">
     <cfRule type="dataBar" priority="16">
